--- a/working/WOBAR_BOOKING_LIST.xlsx
+++ b/working/WOBAR_BOOKING_LIST.xlsx
@@ -4371,11 +4371,23 @@
       <c r="E59" s="17" t="inlineStr"/>
       <c r="F59" s="17" t="inlineStr"/>
       <c r="G59" s="17" t="inlineStr"/>
-      <c r="H59" s="17" t="inlineStr"/>
+      <c r="H59" s="17" t="inlineStr">
+        <is>
+          <t>66,795</t>
+        </is>
+      </c>
       <c r="I59" s="17" t="inlineStr"/>
       <c r="J59" s="17" t="inlineStr"/>
-      <c r="K59" s="32" t="n"/>
-      <c r="L59" s="32" t="inlineStr"/>
+      <c r="K59" s="39" t="inlineStr">
+        <is>
+          <t>Top result 'Zero' - high confidence but not name-exact</t>
+        </is>
+      </c>
+      <c r="L59" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M59" s="32" t="n"/>
       <c r="N59" s="32" t="n"/>
       <c r="O59" s="17" t="inlineStr"/>
@@ -4414,11 +4426,23 @@
       <c r="E60" s="17" t="inlineStr"/>
       <c r="F60" s="17" t="inlineStr"/>
       <c r="G60" s="17" t="inlineStr"/>
-      <c r="H60" s="17" t="inlineStr"/>
+      <c r="H60" s="17" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
       <c r="I60" s="17" t="inlineStr"/>
       <c r="J60" s="17" t="inlineStr"/>
-      <c r="K60" s="32" t="n"/>
-      <c r="L60" s="32" t="inlineStr"/>
+      <c r="K60" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L60" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M60" s="32" t="n"/>
       <c r="N60" s="32" t="n"/>
       <c r="O60" s="17" t="inlineStr"/>
@@ -4457,11 +4481,23 @@
       <c r="E61" s="17" t="inlineStr"/>
       <c r="F61" s="17" t="inlineStr"/>
       <c r="G61" s="17" t="inlineStr"/>
-      <c r="H61" s="17" t="inlineStr"/>
+      <c r="H61" s="17" t="inlineStr">
+        <is>
+          <t>77,724</t>
+        </is>
+      </c>
       <c r="I61" s="17" t="inlineStr"/>
       <c r="J61" s="17" t="inlineStr"/>
-      <c r="K61" s="32" t="n"/>
-      <c r="L61" s="32" t="inlineStr"/>
+      <c r="K61" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L61" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M61" s="32" t="n"/>
       <c r="N61" s="32" t="n"/>
       <c r="O61" s="17" t="inlineStr"/>
@@ -4500,11 +4536,23 @@
       <c r="E62" s="17" t="inlineStr"/>
       <c r="F62" s="17" t="inlineStr"/>
       <c r="G62" s="17" t="inlineStr"/>
-      <c r="H62" s="17" t="inlineStr"/>
+      <c r="H62" s="17" t="inlineStr">
+        <is>
+          <t>97,664</t>
+        </is>
+      </c>
       <c r="I62" s="17" t="inlineStr"/>
       <c r="J62" s="17" t="inlineStr"/>
-      <c r="K62" s="32" t="n"/>
-      <c r="L62" s="32" t="inlineStr"/>
+      <c r="K62" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L62" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M62" s="32" t="n"/>
       <c r="N62" s="32" t="n"/>
       <c r="O62" s="17" t="inlineStr"/>
@@ -4543,11 +4591,23 @@
       <c r="E63" s="17" t="inlineStr"/>
       <c r="F63" s="17" t="inlineStr"/>
       <c r="G63" s="17" t="inlineStr"/>
-      <c r="H63" s="17" t="inlineStr"/>
+      <c r="H63" s="17" t="inlineStr">
+        <is>
+          <t>19,631</t>
+        </is>
+      </c>
       <c r="I63" s="17" t="inlineStr"/>
       <c r="J63" s="17" t="inlineStr"/>
-      <c r="K63" s="32" t="n"/>
-      <c r="L63" s="32" t="inlineStr"/>
+      <c r="K63" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L63" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M63" s="32" t="n"/>
       <c r="N63" s="32" t="n"/>
       <c r="O63" s="17" t="inlineStr"/>
@@ -4586,11 +4646,23 @@
       <c r="E64" s="17" t="inlineStr"/>
       <c r="F64" s="17" t="inlineStr"/>
       <c r="G64" s="17" t="inlineStr"/>
-      <c r="H64" s="17" t="inlineStr"/>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
+          <t>4,886</t>
+        </is>
+      </c>
       <c r="I64" s="17" t="inlineStr"/>
       <c r="J64" s="17" t="inlineStr"/>
-      <c r="K64" s="32" t="n"/>
-      <c r="L64" s="32" t="inlineStr"/>
+      <c r="K64" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L64" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M64" s="32" t="n"/>
       <c r="N64" s="32" t="n"/>
       <c r="O64" s="17" t="inlineStr"/>
@@ -4629,11 +4701,23 @@
       <c r="E65" s="17" t="inlineStr"/>
       <c r="F65" s="17" t="inlineStr"/>
       <c r="G65" s="17" t="inlineStr"/>
-      <c r="H65" s="17" t="inlineStr"/>
+      <c r="H65" s="17" t="inlineStr">
+        <is>
+          <t>8,333</t>
+        </is>
+      </c>
       <c r="I65" s="17" t="inlineStr"/>
       <c r="J65" s="17" t="inlineStr"/>
-      <c r="K65" s="32" t="n"/>
-      <c r="L65" s="32" t="inlineStr"/>
+      <c r="K65" s="39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS - 'Klo' 8,333 vs 'K.L.O' 13,849; took the lower. Verify</t>
+        </is>
+      </c>
+      <c r="L65" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M65" s="32" t="n"/>
       <c r="N65" s="32" t="n"/>
       <c r="O65" s="17" t="inlineStr"/>
@@ -4676,11 +4760,23 @@
       <c r="E66" s="17" t="inlineStr"/>
       <c r="F66" s="17" t="inlineStr"/>
       <c r="G66" s="17" t="inlineStr"/>
-      <c r="H66" s="17" t="inlineStr"/>
+      <c r="H66" s="17" t="inlineStr">
+        <is>
+          <t>8,863</t>
+        </is>
+      </c>
       <c r="I66" s="17" t="inlineStr"/>
       <c r="J66" s="17" t="inlineStr"/>
-      <c r="K66" s="32" t="n"/>
-      <c r="L66" s="32" t="inlineStr"/>
+      <c r="K66" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L66" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M66" s="32" t="n"/>
       <c r="N66" s="32" t="n"/>
       <c r="O66" s="17" t="inlineStr"/>
@@ -4719,11 +4815,23 @@
       <c r="E67" s="17" t="inlineStr"/>
       <c r="F67" s="17" t="inlineStr"/>
       <c r="G67" s="17" t="inlineStr"/>
-      <c r="H67" s="17" t="inlineStr"/>
+      <c r="H67" s="17" t="inlineStr">
+        <is>
+          <t>19,855</t>
+        </is>
+      </c>
       <c r="I67" s="17" t="inlineStr"/>
       <c r="J67" s="17" t="inlineStr"/>
-      <c r="K67" s="32" t="n"/>
-      <c r="L67" s="32" t="inlineStr"/>
+      <c r="K67" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L67" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M67" s="32" t="n"/>
       <c r="N67" s="32" t="n"/>
       <c r="O67" s="17" t="inlineStr"/>
@@ -4762,11 +4870,23 @@
       <c r="E68" s="17" t="inlineStr"/>
       <c r="F68" s="17" t="inlineStr"/>
       <c r="G68" s="17" t="inlineStr"/>
-      <c r="H68" s="17" t="inlineStr"/>
+      <c r="H68" s="17" t="inlineStr">
+        <is>
+          <t>2,961</t>
+        </is>
+      </c>
       <c r="I68" s="17" t="inlineStr"/>
       <c r="J68" s="17" t="inlineStr"/>
-      <c r="K68" s="32" t="n"/>
-      <c r="L68" s="32" t="inlineStr"/>
+      <c r="K68" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L68" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M68" s="32" t="n"/>
       <c r="N68" s="32" t="n"/>
       <c r="O68" s="17" t="inlineStr"/>
@@ -4808,7 +4928,11 @@
       <c r="H69" s="17" t="inlineStr"/>
       <c r="I69" s="17" t="inlineStr"/>
       <c r="J69" s="17" t="inlineStr"/>
-      <c r="K69" s="32" t="n"/>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
       <c r="L69" s="32" t="inlineStr"/>
       <c r="M69" s="32" t="n"/>
       <c r="N69" s="32" t="n"/>
@@ -4848,11 +4972,23 @@
       <c r="E70" s="17" t="inlineStr"/>
       <c r="F70" s="17" t="inlineStr"/>
       <c r="G70" s="17" t="inlineStr"/>
-      <c r="H70" s="17" t="inlineStr"/>
+      <c r="H70" s="17" t="inlineStr">
+        <is>
+          <t>11,160</t>
+        </is>
+      </c>
       <c r="I70" s="17" t="inlineStr"/>
       <c r="J70" s="17" t="inlineStr"/>
-      <c r="K70" s="32" t="n"/>
-      <c r="L70" s="32" t="inlineStr"/>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L70" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M70" s="32" t="n"/>
       <c r="N70" s="32" t="n"/>
       <c r="O70" s="17" t="inlineStr"/>
@@ -4894,7 +5030,11 @@
       <c r="H71" s="17" t="inlineStr"/>
       <c r="I71" s="17" t="inlineStr"/>
       <c r="J71" s="17" t="inlineStr"/>
-      <c r="K71" s="32" t="n"/>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
       <c r="L71" s="32" t="inlineStr"/>
       <c r="M71" s="32" t="n"/>
       <c r="N71" s="32" t="n"/>
@@ -4934,11 +5074,23 @@
       <c r="E72" s="17" t="inlineStr"/>
       <c r="F72" s="17" t="inlineStr"/>
       <c r="G72" s="17" t="inlineStr"/>
-      <c r="H72" s="17" t="inlineStr"/>
+      <c r="H72" s="17" t="inlineStr">
+        <is>
+          <t>55,058</t>
+        </is>
+      </c>
       <c r="I72" s="17" t="inlineStr"/>
       <c r="J72" s="17" t="inlineStr"/>
-      <c r="K72" s="32" t="n"/>
-      <c r="L72" s="32" t="inlineStr"/>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L72" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M72" s="32" t="n"/>
       <c r="N72" s="32" t="n"/>
       <c r="O72" s="17" t="inlineStr"/>
@@ -4981,11 +5133,23 @@
       <c r="E73" s="17" t="inlineStr"/>
       <c r="F73" s="17" t="inlineStr"/>
       <c r="G73" s="17" t="inlineStr"/>
-      <c r="H73" s="17" t="inlineStr"/>
+      <c r="H73" s="17" t="inlineStr">
+        <is>
+          <t>10,336</t>
+        </is>
+      </c>
       <c r="I73" s="17" t="inlineStr"/>
       <c r="J73" s="17" t="inlineStr"/>
-      <c r="K73" s="32" t="n"/>
-      <c r="L73" s="32" t="inlineStr"/>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L73" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M73" s="32" t="n"/>
       <c r="N73" s="32" t="n"/>
       <c r="O73" s="17" t="inlineStr"/>
@@ -5028,11 +5192,23 @@
       <c r="E74" s="17" t="inlineStr"/>
       <c r="F74" s="17" t="inlineStr"/>
       <c r="G74" s="17" t="inlineStr"/>
-      <c r="H74" s="17" t="inlineStr"/>
+      <c r="H74" s="17" t="inlineStr">
+        <is>
+          <t>63,762</t>
+        </is>
+      </c>
       <c r="I74" s="17" t="inlineStr"/>
       <c r="J74" s="17" t="inlineStr"/>
-      <c r="K74" s="32" t="n"/>
-      <c r="L74" s="32" t="inlineStr"/>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L74" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M74" s="32" t="n"/>
       <c r="N74" s="32" t="n"/>
       <c r="O74" s="17" t="inlineStr"/>
@@ -5074,7 +5250,11 @@
       <c r="H75" s="17" t="inlineStr"/>
       <c r="I75" s="17" t="inlineStr"/>
       <c r="J75" s="17" t="inlineStr"/>
-      <c r="K75" s="32" t="n"/>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
       <c r="L75" s="32" t="inlineStr"/>
       <c r="M75" s="32" t="n"/>
       <c r="N75" s="32" t="n"/>
@@ -5114,11 +5294,23 @@
       <c r="E76" s="17" t="inlineStr"/>
       <c r="F76" s="17" t="inlineStr"/>
       <c r="G76" s="17" t="inlineStr"/>
-      <c r="H76" s="17" t="inlineStr"/>
+      <c r="H76" s="17" t="inlineStr">
+        <is>
+          <t>20,145</t>
+        </is>
+      </c>
       <c r="I76" s="17" t="inlineStr"/>
       <c r="J76" s="17" t="inlineStr"/>
-      <c r="K76" s="32" t="n"/>
-      <c r="L76" s="32" t="inlineStr"/>
+      <c r="K76" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L76" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M76" s="32" t="n"/>
       <c r="N76" s="32" t="n"/>
       <c r="O76" s="17" t="inlineStr"/>
@@ -5157,11 +5349,23 @@
       <c r="E77" s="17" t="inlineStr"/>
       <c r="F77" s="17" t="inlineStr"/>
       <c r="G77" s="17" t="inlineStr"/>
-      <c r="H77" s="17" t="inlineStr"/>
+      <c r="H77" s="17" t="inlineStr">
+        <is>
+          <t>42,337</t>
+        </is>
+      </c>
       <c r="I77" s="17" t="inlineStr"/>
       <c r="J77" s="17" t="inlineStr"/>
-      <c r="K77" s="32" t="n"/>
-      <c r="L77" s="32" t="inlineStr"/>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L77" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M77" s="32" t="n"/>
       <c r="N77" s="32" t="n"/>
       <c r="O77" s="17" t="inlineStr"/>
@@ -5200,11 +5404,23 @@
       <c r="E78" s="17" t="inlineStr"/>
       <c r="F78" s="17" t="inlineStr"/>
       <c r="G78" s="17" t="inlineStr"/>
-      <c r="H78" s="17" t="inlineStr"/>
+      <c r="H78" s="17" t="inlineStr">
+        <is>
+          <t>39,313</t>
+        </is>
+      </c>
       <c r="I78" s="17" t="inlineStr"/>
       <c r="J78" s="17" t="inlineStr"/>
-      <c r="K78" s="32" t="n"/>
-      <c r="L78" s="32" t="inlineStr"/>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L78" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M78" s="32" t="n"/>
       <c r="N78" s="32" t="n"/>
       <c r="O78" s="17" t="inlineStr"/>
@@ -5243,11 +5459,23 @@
       <c r="E79" s="17" t="inlineStr"/>
       <c r="F79" s="17" t="inlineStr"/>
       <c r="G79" s="17" t="inlineStr"/>
-      <c r="H79" s="17" t="inlineStr"/>
+      <c r="H79" s="17" t="inlineStr">
+        <is>
+          <t>12,016</t>
+        </is>
+      </c>
       <c r="I79" s="17" t="inlineStr"/>
       <c r="J79" s="17" t="inlineStr"/>
-      <c r="K79" s="32" t="n"/>
-      <c r="L79" s="32" t="inlineStr"/>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L79" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M79" s="32" t="n"/>
       <c r="N79" s="32" t="n"/>
       <c r="O79" s="17" t="inlineStr"/>
@@ -5286,11 +5514,23 @@
       <c r="E80" s="17" t="inlineStr"/>
       <c r="F80" s="17" t="inlineStr"/>
       <c r="G80" s="17" t="inlineStr"/>
-      <c r="H80" s="17" t="inlineStr"/>
+      <c r="H80" s="17" t="inlineStr">
+        <is>
+          <t>50,190</t>
+        </is>
+      </c>
       <c r="I80" s="17" t="inlineStr"/>
       <c r="J80" s="17" t="inlineStr"/>
-      <c r="K80" s="32" t="n"/>
-      <c r="L80" s="32" t="inlineStr"/>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L80" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M80" s="32" t="n"/>
       <c r="N80" s="32" t="n"/>
       <c r="O80" s="17" t="inlineStr"/>
@@ -5329,11 +5569,23 @@
       <c r="E81" s="17" t="inlineStr"/>
       <c r="F81" s="17" t="inlineStr"/>
       <c r="G81" s="17" t="inlineStr"/>
-      <c r="H81" s="17" t="inlineStr"/>
+      <c r="H81" s="17" t="inlineStr">
+        <is>
+          <t>18,678</t>
+        </is>
+      </c>
       <c r="I81" s="17" t="inlineStr"/>
       <c r="J81" s="17" t="inlineStr"/>
-      <c r="K81" s="32" t="n"/>
-      <c r="L81" s="32" t="inlineStr"/>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L81" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M81" s="32" t="n"/>
       <c r="N81" s="32" t="n"/>
       <c r="O81" s="17" t="inlineStr"/>
@@ -5372,11 +5624,23 @@
       <c r="E82" s="17" t="inlineStr"/>
       <c r="F82" s="17" t="inlineStr"/>
       <c r="G82" s="17" t="inlineStr"/>
-      <c r="H82" s="17" t="inlineStr"/>
+      <c r="H82" s="17" t="inlineStr">
+        <is>
+          <t>40,783</t>
+        </is>
+      </c>
       <c r="I82" s="17" t="inlineStr"/>
       <c r="J82" s="17" t="inlineStr"/>
-      <c r="K82" s="32" t="n"/>
-      <c r="L82" s="32" t="inlineStr"/>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L82" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M82" s="7" t="inlineStr">
         <is>
           <t>IN ORBIT: Of The Trees 25x</t>
@@ -5419,11 +5683,23 @@
       <c r="E83" s="17" t="inlineStr"/>
       <c r="F83" s="17" t="inlineStr"/>
       <c r="G83" s="17" t="inlineStr"/>
-      <c r="H83" s="17" t="inlineStr"/>
+      <c r="H83" s="17" t="inlineStr">
+        <is>
+          <t>39,670</t>
+        </is>
+      </c>
       <c r="I83" s="17" t="inlineStr"/>
       <c r="J83" s="17" t="inlineStr"/>
-      <c r="K83" s="32" t="n"/>
-      <c r="L83" s="32" t="inlineStr"/>
+      <c r="K83" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L83" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M83" s="32" t="n"/>
       <c r="N83" s="32" t="n"/>
       <c r="O83" s="17" t="inlineStr"/>
@@ -5462,11 +5738,23 @@
       <c r="E84" s="20" t="inlineStr"/>
       <c r="F84" s="20" t="inlineStr"/>
       <c r="G84" s="20" t="inlineStr"/>
-      <c r="H84" s="20" t="inlineStr"/>
+      <c r="H84" s="20" t="inlineStr">
+        <is>
+          <t>17,153</t>
+        </is>
+      </c>
       <c r="I84" s="20" t="inlineStr"/>
       <c r="J84" s="20" t="inlineStr"/>
-      <c r="K84" s="32" t="n"/>
-      <c r="L84" s="32" t="inlineStr"/>
+      <c r="K84" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L84" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M84" s="32" t="n"/>
       <c r="N84" s="32" t="n"/>
       <c r="O84" s="20" t="inlineStr"/>
@@ -5505,11 +5793,23 @@
       <c r="E85" s="20" t="inlineStr"/>
       <c r="F85" s="20" t="inlineStr"/>
       <c r="G85" s="20" t="inlineStr"/>
-      <c r="H85" s="20" t="inlineStr"/>
+      <c r="H85" s="20" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
       <c r="I85" s="20" t="inlineStr"/>
       <c r="J85" s="20" t="inlineStr"/>
-      <c r="K85" s="32" t="n"/>
-      <c r="L85" s="32" t="inlineStr"/>
+      <c r="K85" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L85" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M85" s="32" t="n"/>
       <c r="N85" s="32" t="n"/>
       <c r="O85" s="20" t="inlineStr"/>
@@ -5548,11 +5848,23 @@
       <c r="E86" s="20" t="inlineStr"/>
       <c r="F86" s="20" t="inlineStr"/>
       <c r="G86" s="20" t="inlineStr"/>
-      <c r="H86" s="20" t="inlineStr"/>
+      <c r="H86" s="20" t="inlineStr">
+        <is>
+          <t>9,267</t>
+        </is>
+      </c>
       <c r="I86" s="20" t="inlineStr"/>
       <c r="J86" s="20" t="inlineStr"/>
-      <c r="K86" s="32" t="n"/>
-      <c r="L86" s="32" t="inlineStr"/>
+      <c r="K86" s="39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS - matched 'Baby Gho$t', different spelling. Verify</t>
+        </is>
+      </c>
+      <c r="L86" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M86" s="32" t="n"/>
       <c r="N86" s="32" t="n"/>
       <c r="O86" s="20" t="inlineStr"/>
@@ -5591,11 +5903,23 @@
       <c r="E87" s="20" t="inlineStr"/>
       <c r="F87" s="20" t="inlineStr"/>
       <c r="G87" s="20" t="inlineStr"/>
-      <c r="H87" s="20" t="inlineStr"/>
+      <c r="H87" s="20" t="inlineStr">
+        <is>
+          <t>1,634</t>
+        </is>
+      </c>
       <c r="I87" s="20" t="inlineStr"/>
       <c r="J87" s="20" t="inlineStr"/>
-      <c r="K87" s="32" t="n"/>
-      <c r="L87" s="32" t="inlineStr"/>
+      <c r="K87" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L87" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M87" s="32" t="n"/>
       <c r="N87" s="32" t="n"/>
       <c r="O87" s="20" t="inlineStr"/>
@@ -5634,11 +5958,23 @@
       <c r="E88" s="20" t="inlineStr"/>
       <c r="F88" s="20" t="inlineStr"/>
       <c r="G88" s="20" t="inlineStr"/>
-      <c r="H88" s="20" t="inlineStr"/>
+      <c r="H88" s="20" t="inlineStr">
+        <is>
+          <t>3,063</t>
+        </is>
+      </c>
       <c r="I88" s="20" t="inlineStr"/>
       <c r="J88" s="20" t="inlineStr"/>
-      <c r="K88" s="32" t="n"/>
-      <c r="L88" s="32" t="inlineStr"/>
+      <c r="K88" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L88" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M88" s="32" t="n"/>
       <c r="N88" s="32" t="n"/>
       <c r="O88" s="20" t="inlineStr"/>
@@ -5677,11 +6013,23 @@
       <c r="E89" s="20" t="inlineStr"/>
       <c r="F89" s="20" t="inlineStr"/>
       <c r="G89" s="20" t="inlineStr"/>
-      <c r="H89" s="20" t="inlineStr"/>
+      <c r="H89" s="20" t="inlineStr">
+        <is>
+          <t>2,230</t>
+        </is>
+      </c>
       <c r="I89" s="20" t="inlineStr"/>
       <c r="J89" s="20" t="inlineStr"/>
-      <c r="K89" s="32" t="n"/>
-      <c r="L89" s="32" t="inlineStr"/>
+      <c r="K89" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L89" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M89" s="32" t="n"/>
       <c r="N89" s="32" t="n"/>
       <c r="O89" s="20" t="inlineStr"/>
@@ -5720,11 +6068,23 @@
       <c r="E90" s="20" t="inlineStr"/>
       <c r="F90" s="20" t="inlineStr"/>
       <c r="G90" s="20" t="inlineStr"/>
-      <c r="H90" s="20" t="inlineStr"/>
+      <c r="H90" s="20" t="inlineStr">
+        <is>
+          <t>172,114</t>
+        </is>
+      </c>
       <c r="I90" s="20" t="inlineStr"/>
       <c r="J90" s="20" t="inlineStr"/>
-      <c r="K90" s="32" t="n"/>
-      <c r="L90" s="32" t="inlineStr"/>
+      <c r="K90" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L90" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M90" s="7" t="inlineStr">
         <is>
           <t>HUB x2: Of The Trees 37x + LSDREAM 61x. Runs Odyzey</t>
@@ -5767,11 +6127,23 @@
       <c r="E91" s="20" t="inlineStr"/>
       <c r="F91" s="20" t="inlineStr"/>
       <c r="G91" s="20" t="inlineStr"/>
-      <c r="H91" s="20" t="inlineStr"/>
+      <c r="H91" s="20" t="inlineStr">
+        <is>
+          <t>17,004</t>
+        </is>
+      </c>
       <c r="I91" s="20" t="inlineStr"/>
       <c r="J91" s="20" t="inlineStr"/>
-      <c r="K91" s="32" t="n"/>
-      <c r="L91" s="32" t="inlineStr"/>
+      <c r="K91" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L91" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M91" s="32" t="n"/>
       <c r="N91" s="32" t="n"/>
       <c r="O91" s="20" t="inlineStr"/>
@@ -5810,11 +6182,23 @@
       <c r="E92" s="20" t="inlineStr"/>
       <c r="F92" s="20" t="inlineStr"/>
       <c r="G92" s="20" t="inlineStr"/>
-      <c r="H92" s="20" t="inlineStr"/>
+      <c r="H92" s="20" t="inlineStr">
+        <is>
+          <t>71,216</t>
+        </is>
+      </c>
       <c r="I92" s="20" t="inlineStr"/>
       <c r="J92" s="20" t="inlineStr"/>
-      <c r="K92" s="32" t="n"/>
-      <c r="L92" s="32" t="inlineStr"/>
+      <c r="K92" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L92" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M92" s="32" t="n"/>
       <c r="N92" s="32" t="n"/>
       <c r="O92" s="20" t="inlineStr"/>
@@ -5853,11 +6237,23 @@
       <c r="E93" s="20" t="inlineStr"/>
       <c r="F93" s="20" t="inlineStr"/>
       <c r="G93" s="20" t="inlineStr"/>
-      <c r="H93" s="20" t="inlineStr"/>
+      <c r="H93" s="20" t="inlineStr">
+        <is>
+          <t>46,849</t>
+        </is>
+      </c>
       <c r="I93" s="20" t="inlineStr"/>
       <c r="J93" s="20" t="inlineStr"/>
-      <c r="K93" s="32" t="n"/>
-      <c r="L93" s="32" t="inlineStr"/>
+      <c r="K93" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L93" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M93" s="32" t="n"/>
       <c r="N93" s="32" t="n"/>
       <c r="O93" s="20" t="inlineStr"/>
@@ -5896,11 +6292,23 @@
       <c r="E94" s="20" t="inlineStr"/>
       <c r="F94" s="20" t="inlineStr"/>
       <c r="G94" s="20" t="inlineStr"/>
-      <c r="H94" s="20" t="inlineStr"/>
+      <c r="H94" s="20" t="inlineStr">
+        <is>
+          <t>4,984</t>
+        </is>
+      </c>
       <c r="I94" s="20" t="inlineStr"/>
       <c r="J94" s="20" t="inlineStr"/>
-      <c r="K94" s="32" t="n"/>
-      <c r="L94" s="32" t="inlineStr"/>
+      <c r="K94" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L94" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M94" s="32" t="n"/>
       <c r="N94" s="32" t="n"/>
       <c r="O94" s="20" t="inlineStr"/>
@@ -5939,11 +6347,23 @@
       <c r="E95" s="20" t="inlineStr"/>
       <c r="F95" s="20" t="inlineStr"/>
       <c r="G95" s="20" t="inlineStr"/>
-      <c r="H95" s="20" t="inlineStr"/>
+      <c r="H95" s="20" t="inlineStr">
+        <is>
+          <t>4,091</t>
+        </is>
+      </c>
       <c r="I95" s="20" t="inlineStr"/>
       <c r="J95" s="20" t="inlineStr"/>
-      <c r="K95" s="32" t="n"/>
-      <c r="L95" s="32" t="inlineStr"/>
+      <c r="K95" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L95" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M95" s="32" t="n"/>
       <c r="N95" s="32" t="n"/>
       <c r="O95" s="20" t="inlineStr"/>
@@ -5982,11 +6402,23 @@
       <c r="E96" s="20" t="inlineStr"/>
       <c r="F96" s="20" t="inlineStr"/>
       <c r="G96" s="20" t="inlineStr"/>
-      <c r="H96" s="20" t="inlineStr"/>
+      <c r="H96" s="20" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
       <c r="I96" s="20" t="inlineStr"/>
       <c r="J96" s="20" t="inlineStr"/>
-      <c r="K96" s="32" t="n"/>
-      <c r="L96" s="32" t="inlineStr"/>
+      <c r="K96" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L96" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M96" s="32" t="n"/>
       <c r="N96" s="32" t="n"/>
       <c r="O96" s="20" t="inlineStr"/>
@@ -6025,11 +6457,23 @@
       <c r="E97" s="20" t="inlineStr"/>
       <c r="F97" s="20" t="inlineStr"/>
       <c r="G97" s="20" t="inlineStr"/>
-      <c r="H97" s="20" t="inlineStr"/>
+      <c r="H97" s="20" t="inlineStr">
+        <is>
+          <t>5,459</t>
+        </is>
+      </c>
       <c r="I97" s="20" t="inlineStr"/>
       <c r="J97" s="20" t="inlineStr"/>
-      <c r="K97" s="32" t="n"/>
-      <c r="L97" s="32" t="inlineStr"/>
+      <c r="K97" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L97" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M97" s="32" t="n"/>
       <c r="N97" s="32" t="n"/>
       <c r="O97" s="20" t="inlineStr"/>
@@ -6068,11 +6512,23 @@
       <c r="E98" s="20" t="inlineStr"/>
       <c r="F98" s="20" t="inlineStr"/>
       <c r="G98" s="20" t="inlineStr"/>
-      <c r="H98" s="20" t="inlineStr"/>
+      <c r="H98" s="20" t="inlineStr">
+        <is>
+          <t>1,918</t>
+        </is>
+      </c>
       <c r="I98" s="20" t="inlineStr"/>
       <c r="J98" s="20" t="inlineStr"/>
-      <c r="K98" s="32" t="n"/>
-      <c r="L98" s="32" t="inlineStr"/>
+      <c r="K98" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L98" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M98" s="32" t="n"/>
       <c r="N98" s="32" t="n"/>
       <c r="O98" s="20" t="inlineStr"/>
@@ -6111,11 +6567,23 @@
       <c r="E99" s="20" t="inlineStr"/>
       <c r="F99" s="20" t="inlineStr"/>
       <c r="G99" s="20" t="inlineStr"/>
-      <c r="H99" s="20" t="inlineStr"/>
+      <c r="H99" s="20" t="inlineStr">
+        <is>
+          <t>4,839</t>
+        </is>
+      </c>
       <c r="I99" s="20" t="inlineStr"/>
       <c r="J99" s="20" t="inlineStr"/>
-      <c r="K99" s="32" t="n"/>
-      <c r="L99" s="32" t="inlineStr"/>
+      <c r="K99" s="39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS - matched 'HomeSick' (verified), different spelling. Verify</t>
+        </is>
+      </c>
+      <c r="L99" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M99" s="32" t="n"/>
       <c r="N99" s="32" t="n"/>
       <c r="O99" s="20" t="inlineStr"/>
@@ -6154,11 +6622,23 @@
       <c r="E100" s="20" t="inlineStr"/>
       <c r="F100" s="20" t="inlineStr"/>
       <c r="G100" s="20" t="inlineStr"/>
-      <c r="H100" s="20" t="inlineStr"/>
+      <c r="H100" s="20" t="inlineStr">
+        <is>
+          <t>7,166</t>
+        </is>
+      </c>
       <c r="I100" s="20" t="inlineStr"/>
       <c r="J100" s="20" t="inlineStr"/>
-      <c r="K100" s="32" t="n"/>
-      <c r="L100" s="32" t="inlineStr"/>
+      <c r="K100" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L100" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M100" s="32" t="n"/>
       <c r="N100" s="32" t="n"/>
       <c r="O100" s="20" t="inlineStr"/>
@@ -6197,11 +6677,23 @@
       <c r="E101" s="20" t="inlineStr"/>
       <c r="F101" s="20" t="inlineStr"/>
       <c r="G101" s="20" t="inlineStr"/>
-      <c r="H101" s="20" t="inlineStr"/>
+      <c r="H101" s="20" t="inlineStr">
+        <is>
+          <t>5,676</t>
+        </is>
+      </c>
       <c r="I101" s="20" t="inlineStr"/>
       <c r="J101" s="20" t="inlineStr"/>
-      <c r="K101" s="32" t="n"/>
-      <c r="L101" s="32" t="inlineStr"/>
+      <c r="K101" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L101" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M101" s="32" t="n"/>
       <c r="N101" s="32" t="n"/>
       <c r="O101" s="20" t="inlineStr"/>
@@ -6240,11 +6732,23 @@
       <c r="E102" s="20" t="inlineStr"/>
       <c r="F102" s="20" t="inlineStr"/>
       <c r="G102" s="20" t="inlineStr"/>
-      <c r="H102" s="20" t="inlineStr"/>
+      <c r="H102" s="20" t="inlineStr">
+        <is>
+          <t>16,193</t>
+        </is>
+      </c>
       <c r="I102" s="20" t="inlineStr"/>
       <c r="J102" s="20" t="inlineStr"/>
-      <c r="K102" s="32" t="n"/>
-      <c r="L102" s="32" t="inlineStr"/>
+      <c r="K102" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L102" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M102" s="32" t="n"/>
       <c r="N102" s="32" t="n"/>
       <c r="O102" s="20" t="inlineStr"/>
@@ -6283,11 +6787,23 @@
       <c r="E103" s="20" t="inlineStr"/>
       <c r="F103" s="20" t="inlineStr"/>
       <c r="G103" s="20" t="inlineStr"/>
-      <c r="H103" s="20" t="inlineStr"/>
+      <c r="H103" s="20" t="inlineStr">
+        <is>
+          <t>9,086</t>
+        </is>
+      </c>
       <c r="I103" s="20" t="inlineStr"/>
       <c r="J103" s="20" t="inlineStr"/>
-      <c r="K103" s="32" t="n"/>
-      <c r="L103" s="32" t="inlineStr"/>
+      <c r="K103" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L103" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M103" s="32" t="n"/>
       <c r="N103" s="32" t="n"/>
       <c r="O103" s="20" t="inlineStr"/>
@@ -6369,11 +6885,23 @@
       <c r="E105" s="20" t="inlineStr"/>
       <c r="F105" s="20" t="inlineStr"/>
       <c r="G105" s="20" t="inlineStr"/>
-      <c r="H105" s="20" t="inlineStr"/>
+      <c r="H105" s="20" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
       <c r="I105" s="20" t="inlineStr"/>
       <c r="J105" s="20" t="inlineStr"/>
-      <c r="K105" s="32" t="n"/>
-      <c r="L105" s="32" t="inlineStr"/>
+      <c r="K105" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L105" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M105" s="32" t="n"/>
       <c r="N105" s="32" t="n"/>
       <c r="O105" s="20" t="inlineStr"/>
@@ -6458,7 +6986,11 @@
       <c r="H107" s="20" t="inlineStr"/>
       <c r="I107" s="20" t="inlineStr"/>
       <c r="J107" s="20" t="inlineStr"/>
-      <c r="K107" s="32" t="n"/>
+      <c r="K107" s="39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS - collides with the UK grime artist Wiley. Name search unsafe; needs handle resolution</t>
+        </is>
+      </c>
       <c r="L107" s="32" t="inlineStr"/>
       <c r="M107" s="32" t="n"/>
       <c r="N107" s="32" t="n"/>
@@ -6498,11 +7030,23 @@
       <c r="E108" s="20" t="inlineStr"/>
       <c r="F108" s="20" t="inlineStr"/>
       <c r="G108" s="20" t="inlineStr"/>
-      <c r="H108" s="20" t="inlineStr"/>
+      <c r="H108" s="20" t="inlineStr">
+        <is>
+          <t>8,223</t>
+        </is>
+      </c>
       <c r="I108" s="20" t="inlineStr"/>
       <c r="J108" s="20" t="inlineStr"/>
-      <c r="K108" s="32" t="n"/>
-      <c r="L108" s="32" t="inlineStr"/>
+      <c r="K108" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L108" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M108" s="32" t="n"/>
       <c r="N108" s="32" t="n"/>
       <c r="O108" s="20" t="inlineStr"/>
@@ -6541,11 +7085,23 @@
       <c r="E109" s="20" t="inlineStr"/>
       <c r="F109" s="20" t="inlineStr"/>
       <c r="G109" s="20" t="inlineStr"/>
-      <c r="H109" s="20" t="inlineStr"/>
+      <c r="H109" s="20" t="inlineStr">
+        <is>
+          <t>5,718</t>
+        </is>
+      </c>
       <c r="I109" s="20" t="inlineStr"/>
       <c r="J109" s="20" t="inlineStr"/>
-      <c r="K109" s="32" t="n"/>
-      <c r="L109" s="32" t="inlineStr"/>
+      <c r="K109" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L109" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M109" s="32" t="n"/>
       <c r="N109" s="32" t="n"/>
       <c r="O109" s="20" t="inlineStr"/>
@@ -6584,11 +7140,23 @@
       <c r="E110" s="20" t="inlineStr"/>
       <c r="F110" s="20" t="inlineStr"/>
       <c r="G110" s="20" t="inlineStr"/>
-      <c r="H110" s="20" t="inlineStr"/>
+      <c r="H110" s="20" t="inlineStr">
+        <is>
+          <t>18,141</t>
+        </is>
+      </c>
       <c r="I110" s="20" t="inlineStr"/>
       <c r="J110" s="20" t="inlineStr"/>
-      <c r="K110" s="32" t="n"/>
-      <c r="L110" s="32" t="inlineStr"/>
+      <c r="K110" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L110" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M110" s="32" t="n"/>
       <c r="N110" s="32" t="n"/>
       <c r="O110" s="20" t="inlineStr"/>
@@ -6627,11 +7195,23 @@
       <c r="E111" s="20" t="inlineStr"/>
       <c r="F111" s="20" t="inlineStr"/>
       <c r="G111" s="20" t="inlineStr"/>
-      <c r="H111" s="20" t="inlineStr"/>
+      <c r="H111" s="20" t="inlineStr">
+        <is>
+          <t>8,646</t>
+        </is>
+      </c>
       <c r="I111" s="20" t="inlineStr"/>
       <c r="J111" s="20" t="inlineStr"/>
-      <c r="K111" s="32" t="n"/>
-      <c r="L111" s="32" t="inlineStr"/>
+      <c r="K111" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L111" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M111" s="32" t="n"/>
       <c r="N111" s="32" t="n"/>
       <c r="O111" s="20" t="inlineStr"/>
@@ -6670,11 +7250,23 @@
       <c r="E112" s="20" t="inlineStr"/>
       <c r="F112" s="20" t="inlineStr"/>
       <c r="G112" s="20" t="inlineStr"/>
-      <c r="H112" s="20" t="inlineStr"/>
+      <c r="H112" s="20" t="inlineStr">
+        <is>
+          <t>8,365</t>
+        </is>
+      </c>
       <c r="I112" s="20" t="inlineStr"/>
       <c r="J112" s="20" t="inlineStr"/>
-      <c r="K112" s="32" t="n"/>
-      <c r="L112" s="32" t="inlineStr"/>
+      <c r="K112" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L112" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M112" s="32" t="n"/>
       <c r="N112" s="32" t="n"/>
       <c r="O112" s="20" t="inlineStr"/>
@@ -6713,11 +7305,23 @@
       <c r="E113" s="20" t="inlineStr"/>
       <c r="F113" s="20" t="inlineStr"/>
       <c r="G113" s="20" t="inlineStr"/>
-      <c r="H113" s="20" t="inlineStr"/>
+      <c r="H113" s="20" t="inlineStr">
+        <is>
+          <t>7,823</t>
+        </is>
+      </c>
       <c r="I113" s="20" t="inlineStr"/>
       <c r="J113" s="20" t="inlineStr"/>
-      <c r="K113" s="32" t="n"/>
-      <c r="L113" s="32" t="inlineStr"/>
+      <c r="K113" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L113" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M113" s="32" t="n"/>
       <c r="N113" s="32" t="n"/>
       <c r="O113" s="20" t="inlineStr"/>
@@ -6756,11 +7360,23 @@
       <c r="E114" s="20" t="inlineStr"/>
       <c r="F114" s="20" t="inlineStr"/>
       <c r="G114" s="20" t="inlineStr"/>
-      <c r="H114" s="20" t="inlineStr"/>
+      <c r="H114" s="20" t="inlineStr">
+        <is>
+          <t>18,196</t>
+        </is>
+      </c>
       <c r="I114" s="20" t="inlineStr"/>
       <c r="J114" s="20" t="inlineStr"/>
-      <c r="K114" s="32" t="n"/>
-      <c r="L114" s="32" t="inlineStr"/>
+      <c r="K114" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L114" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M114" s="32" t="n"/>
       <c r="N114" s="32" t="n"/>
       <c r="O114" s="20" t="inlineStr"/>
@@ -6799,11 +7415,23 @@
       <c r="E115" s="20" t="inlineStr"/>
       <c r="F115" s="20" t="inlineStr"/>
       <c r="G115" s="20" t="inlineStr"/>
-      <c r="H115" s="20" t="inlineStr"/>
+      <c r="H115" s="20" t="inlineStr">
+        <is>
+          <t>7,081</t>
+        </is>
+      </c>
       <c r="I115" s="20" t="inlineStr"/>
       <c r="J115" s="20" t="inlineStr"/>
-      <c r="K115" s="32" t="n"/>
-      <c r="L115" s="32" t="inlineStr"/>
+      <c r="K115" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L115" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M115" s="32" t="n"/>
       <c r="N115" s="32" t="n"/>
       <c r="O115" s="20" t="inlineStr"/>
@@ -6842,11 +7470,23 @@
       <c r="E116" s="20" t="inlineStr"/>
       <c r="F116" s="20" t="inlineStr"/>
       <c r="G116" s="20" t="inlineStr"/>
-      <c r="H116" s="20" t="inlineStr"/>
+      <c r="H116" s="20" t="inlineStr">
+        <is>
+          <t>1,956</t>
+        </is>
+      </c>
       <c r="I116" s="20" t="inlineStr"/>
       <c r="J116" s="20" t="inlineStr"/>
-      <c r="K116" s="32" t="n"/>
-      <c r="L116" s="32" t="inlineStr"/>
+      <c r="K116" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L116" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M116" s="32" t="n"/>
       <c r="N116" s="32" t="n"/>
       <c r="O116" s="20" t="inlineStr"/>
@@ -6885,11 +7525,23 @@
       <c r="E117" s="20" t="inlineStr"/>
       <c r="F117" s="20" t="inlineStr"/>
       <c r="G117" s="20" t="inlineStr"/>
-      <c r="H117" s="20" t="inlineStr"/>
+      <c r="H117" s="20" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
       <c r="I117" s="20" t="inlineStr"/>
       <c r="J117" s="20" t="inlineStr"/>
-      <c r="K117" s="32" t="n"/>
-      <c r="L117" s="32" t="inlineStr"/>
+      <c r="K117" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L117" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M117" s="32" t="n"/>
       <c r="N117" s="32" t="n"/>
       <c r="O117" s="20" t="inlineStr"/>
@@ -6928,11 +7580,23 @@
       <c r="E118" s="20" t="inlineStr"/>
       <c r="F118" s="20" t="inlineStr"/>
       <c r="G118" s="20" t="inlineStr"/>
-      <c r="H118" s="20" t="inlineStr"/>
+      <c r="H118" s="20" t="inlineStr">
+        <is>
+          <t>1,607</t>
+        </is>
+      </c>
       <c r="I118" s="20" t="inlineStr"/>
       <c r="J118" s="20" t="inlineStr"/>
-      <c r="K118" s="32" t="n"/>
-      <c r="L118" s="32" t="inlineStr"/>
+      <c r="K118" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L118" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M118" s="32" t="n"/>
       <c r="N118" s="32" t="n"/>
       <c r="O118" s="20" t="inlineStr"/>
@@ -6971,11 +7635,23 @@
       <c r="E119" s="20" t="inlineStr"/>
       <c r="F119" s="20" t="inlineStr"/>
       <c r="G119" s="20" t="inlineStr"/>
-      <c r="H119" s="20" t="inlineStr"/>
+      <c r="H119" s="20" t="inlineStr">
+        <is>
+          <t>34,485</t>
+        </is>
+      </c>
       <c r="I119" s="20" t="inlineStr"/>
       <c r="J119" s="20" t="inlineStr"/>
-      <c r="K119" s="32" t="n"/>
-      <c r="L119" s="32" t="inlineStr"/>
+      <c r="K119" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L119" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M119" s="32" t="n"/>
       <c r="N119" s="32" t="n"/>
       <c r="O119" s="20" t="inlineStr"/>
@@ -7014,11 +7690,23 @@
       <c r="E120" s="20" t="inlineStr"/>
       <c r="F120" s="20" t="inlineStr"/>
       <c r="G120" s="20" t="inlineStr"/>
-      <c r="H120" s="20" t="inlineStr"/>
+      <c r="H120" s="20" t="inlineStr">
+        <is>
+          <t>221,773</t>
+        </is>
+      </c>
       <c r="I120" s="20" t="inlineStr"/>
       <c r="J120" s="20" t="inlineStr"/>
-      <c r="K120" s="32" t="n"/>
-      <c r="L120" s="32" t="inlineStr"/>
+      <c r="K120" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L120" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M120" s="32" t="n"/>
       <c r="N120" s="32" t="n"/>
       <c r="O120" s="20" t="inlineStr"/>
@@ -7057,11 +7745,23 @@
       <c r="E121" s="20" t="inlineStr"/>
       <c r="F121" s="20" t="inlineStr"/>
       <c r="G121" s="20" t="inlineStr"/>
-      <c r="H121" s="20" t="inlineStr"/>
+      <c r="H121" s="20" t="inlineStr">
+        <is>
+          <t>3,218</t>
+        </is>
+      </c>
       <c r="I121" s="20" t="inlineStr"/>
       <c r="J121" s="20" t="inlineStr"/>
-      <c r="K121" s="32" t="n"/>
-      <c r="L121" s="32" t="inlineStr"/>
+      <c r="K121" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L121" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M121" s="32" t="n"/>
       <c r="N121" s="32" t="n"/>
       <c r="O121" s="20" t="inlineStr"/>
@@ -7143,11 +7843,23 @@
       <c r="E123" s="20" t="inlineStr"/>
       <c r="F123" s="20" t="inlineStr"/>
       <c r="G123" s="20" t="inlineStr"/>
-      <c r="H123" s="20" t="inlineStr"/>
+      <c r="H123" s="20" t="inlineStr">
+        <is>
+          <t>7,626</t>
+        </is>
+      </c>
       <c r="I123" s="20" t="inlineStr"/>
       <c r="J123" s="20" t="inlineStr"/>
-      <c r="K123" s="32" t="n"/>
-      <c r="L123" s="32" t="inlineStr"/>
+      <c r="K123" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L123" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M123" s="32" t="n"/>
       <c r="N123" s="32" t="n"/>
       <c r="O123" s="20" t="inlineStr"/>
@@ -7229,11 +7941,23 @@
       <c r="E125" s="20" t="inlineStr"/>
       <c r="F125" s="20" t="inlineStr"/>
       <c r="G125" s="20" t="inlineStr"/>
-      <c r="H125" s="20" t="inlineStr"/>
+      <c r="H125" s="20" t="inlineStr">
+        <is>
+          <t>4,047</t>
+        </is>
+      </c>
       <c r="I125" s="20" t="inlineStr"/>
       <c r="J125" s="20" t="inlineStr"/>
-      <c r="K125" s="32" t="n"/>
-      <c r="L125" s="32" t="inlineStr"/>
+      <c r="K125" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L125" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M125" s="32" t="n"/>
       <c r="N125" s="32" t="n"/>
       <c r="O125" s="20" t="inlineStr"/>
@@ -7272,11 +7996,23 @@
       <c r="E126" s="20" t="inlineStr"/>
       <c r="F126" s="20" t="inlineStr"/>
       <c r="G126" s="20" t="inlineStr"/>
-      <c r="H126" s="20" t="inlineStr"/>
+      <c r="H126" s="20" t="inlineStr">
+        <is>
+          <t>2,017</t>
+        </is>
+      </c>
       <c r="I126" s="20" t="inlineStr"/>
       <c r="J126" s="20" t="inlineStr"/>
-      <c r="K126" s="32" t="n"/>
-      <c r="L126" s="32" t="inlineStr"/>
+      <c r="K126" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L126" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M126" s="32" t="n"/>
       <c r="N126" s="32" t="n"/>
       <c r="O126" s="20" t="inlineStr"/>
@@ -7401,11 +8137,23 @@
       <c r="E129" s="20" t="inlineStr"/>
       <c r="F129" s="20" t="inlineStr"/>
       <c r="G129" s="20" t="inlineStr"/>
-      <c r="H129" s="20" t="inlineStr"/>
+      <c r="H129" s="20" t="inlineStr">
+        <is>
+          <t>40,068</t>
+        </is>
+      </c>
       <c r="I129" s="20" t="inlineStr"/>
       <c r="J129" s="20" t="inlineStr"/>
-      <c r="K129" s="32" t="n"/>
-      <c r="L129" s="32" t="inlineStr"/>
+      <c r="K129" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L129" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M129" s="32" t="n"/>
       <c r="N129" s="32" t="n"/>
       <c r="O129" s="20" t="inlineStr"/>
@@ -7444,11 +8192,23 @@
       <c r="E130" s="20" t="inlineStr"/>
       <c r="F130" s="20" t="inlineStr"/>
       <c r="G130" s="20" t="inlineStr"/>
-      <c r="H130" s="20" t="inlineStr"/>
+      <c r="H130" s="20" t="inlineStr">
+        <is>
+          <t>32,611</t>
+        </is>
+      </c>
       <c r="I130" s="20" t="inlineStr"/>
       <c r="J130" s="20" t="inlineStr"/>
-      <c r="K130" s="32" t="n"/>
-      <c r="L130" s="32" t="inlineStr"/>
+      <c r="K130" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L130" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M130" s="32" t="n"/>
       <c r="N130" s="32" t="n"/>
       <c r="O130" s="20" t="inlineStr"/>
@@ -7487,11 +8247,23 @@
       <c r="E131" s="20" t="inlineStr"/>
       <c r="F131" s="20" t="inlineStr"/>
       <c r="G131" s="20" t="inlineStr"/>
-      <c r="H131" s="20" t="inlineStr"/>
+      <c r="H131" s="20" t="inlineStr">
+        <is>
+          <t>10,704</t>
+        </is>
+      </c>
       <c r="I131" s="20" t="inlineStr"/>
       <c r="J131" s="20" t="inlineStr"/>
-      <c r="K131" s="32" t="n"/>
-      <c r="L131" s="32" t="inlineStr"/>
+      <c r="K131" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L131" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M131" s="32" t="n"/>
       <c r="N131" s="32" t="n"/>
       <c r="O131" s="20" t="inlineStr"/>
@@ -7530,11 +8302,23 @@
       <c r="E132" s="20" t="inlineStr"/>
       <c r="F132" s="20" t="inlineStr"/>
       <c r="G132" s="20" t="inlineStr"/>
-      <c r="H132" s="20" t="inlineStr"/>
+      <c r="H132" s="20" t="inlineStr">
+        <is>
+          <t>12,565</t>
+        </is>
+      </c>
       <c r="I132" s="20" t="inlineStr"/>
       <c r="J132" s="20" t="inlineStr"/>
-      <c r="K132" s="32" t="n"/>
-      <c r="L132" s="32" t="inlineStr"/>
+      <c r="K132" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L132" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M132" s="32" t="n"/>
       <c r="N132" s="32" t="n"/>
       <c r="O132" s="20" t="inlineStr"/>
@@ -7573,11 +8357,23 @@
       <c r="E133" s="20" t="inlineStr"/>
       <c r="F133" s="20" t="inlineStr"/>
       <c r="G133" s="20" t="inlineStr"/>
-      <c r="H133" s="20" t="inlineStr"/>
+      <c r="H133" s="20" t="inlineStr">
+        <is>
+          <t>1,494</t>
+        </is>
+      </c>
       <c r="I133" s="20" t="inlineStr"/>
       <c r="J133" s="20" t="inlineStr"/>
-      <c r="K133" s="32" t="n"/>
-      <c r="L133" s="32" t="inlineStr"/>
+      <c r="K133" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L133" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M133" s="32" t="n"/>
       <c r="N133" s="32" t="n"/>
       <c r="O133" s="20" t="inlineStr"/>
@@ -7616,11 +8412,23 @@
       <c r="E134" s="20" t="inlineStr"/>
       <c r="F134" s="20" t="inlineStr"/>
       <c r="G134" s="20" t="inlineStr"/>
-      <c r="H134" s="20" t="inlineStr"/>
+      <c r="H134" s="20" t="inlineStr">
+        <is>
+          <t>2,371</t>
+        </is>
+      </c>
       <c r="I134" s="20" t="inlineStr"/>
       <c r="J134" s="20" t="inlineStr"/>
-      <c r="K134" s="32" t="n"/>
-      <c r="L134" s="32" t="inlineStr"/>
+      <c r="K134" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L134" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M134" s="32" t="n"/>
       <c r="N134" s="32" t="n"/>
       <c r="O134" s="20" t="inlineStr"/>
@@ -7659,11 +8467,23 @@
       <c r="E135" s="20" t="inlineStr"/>
       <c r="F135" s="20" t="inlineStr"/>
       <c r="G135" s="20" t="inlineStr"/>
-      <c r="H135" s="20" t="inlineStr"/>
+      <c r="H135" s="20" t="inlineStr">
+        <is>
+          <t>6,124</t>
+        </is>
+      </c>
       <c r="I135" s="20" t="inlineStr"/>
       <c r="J135" s="20" t="inlineStr"/>
-      <c r="K135" s="32" t="n"/>
-      <c r="L135" s="32" t="inlineStr"/>
+      <c r="K135" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L135" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M135" s="32" t="n"/>
       <c r="N135" s="32" t="n"/>
       <c r="O135" s="20" t="inlineStr"/>
@@ -7702,11 +8522,23 @@
       <c r="E136" s="20" t="inlineStr"/>
       <c r="F136" s="20" t="inlineStr"/>
       <c r="G136" s="20" t="inlineStr"/>
-      <c r="H136" s="20" t="inlineStr"/>
+      <c r="H136" s="20" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
       <c r="I136" s="20" t="inlineStr"/>
       <c r="J136" s="20" t="inlineStr"/>
-      <c r="K136" s="32" t="n"/>
-      <c r="L136" s="32" t="inlineStr"/>
+      <c r="K136" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L136" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M136" s="32" t="n"/>
       <c r="N136" s="32" t="n"/>
       <c r="O136" s="20" t="inlineStr"/>
@@ -7745,11 +8577,23 @@
       <c r="E137" s="20" t="inlineStr"/>
       <c r="F137" s="20" t="inlineStr"/>
       <c r="G137" s="20" t="inlineStr"/>
-      <c r="H137" s="20" t="inlineStr"/>
+      <c r="H137" s="20" t="inlineStr">
+        <is>
+          <t>2,093</t>
+        </is>
+      </c>
       <c r="I137" s="20" t="inlineStr"/>
       <c r="J137" s="20" t="inlineStr"/>
-      <c r="K137" s="32" t="n"/>
-      <c r="L137" s="32" t="inlineStr"/>
+      <c r="K137" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L137" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M137" s="32" t="n"/>
       <c r="N137" s="32" t="n"/>
       <c r="O137" s="20" t="inlineStr"/>
@@ -7788,11 +8632,23 @@
       <c r="E138" s="20" t="inlineStr"/>
       <c r="F138" s="20" t="inlineStr"/>
       <c r="G138" s="20" t="inlineStr"/>
-      <c r="H138" s="20" t="inlineStr"/>
+      <c r="H138" s="20" t="inlineStr">
+        <is>
+          <t>57,411</t>
+        </is>
+      </c>
       <c r="I138" s="20" t="inlineStr"/>
       <c r="J138" s="20" t="inlineStr"/>
-      <c r="K138" s="32" t="n"/>
-      <c r="L138" s="32" t="inlineStr"/>
+      <c r="K138" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L138" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M138" s="32" t="n"/>
       <c r="N138" s="32" t="n"/>
       <c r="O138" s="20" t="inlineStr"/>
@@ -7831,11 +8687,23 @@
       <c r="E139" s="20" t="inlineStr"/>
       <c r="F139" s="20" t="inlineStr"/>
       <c r="G139" s="20" t="inlineStr"/>
-      <c r="H139" s="20" t="inlineStr"/>
+      <c r="H139" s="20" t="inlineStr">
+        <is>
+          <t>12,516</t>
+        </is>
+      </c>
       <c r="I139" s="20" t="inlineStr"/>
       <c r="J139" s="20" t="inlineStr"/>
-      <c r="K139" s="32" t="n"/>
-      <c r="L139" s="32" t="inlineStr"/>
+      <c r="K139" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L139" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M139" s="32" t="n"/>
       <c r="N139" s="32" t="n"/>
       <c r="O139" s="20" t="inlineStr"/>
@@ -7874,11 +8742,23 @@
       <c r="E140" s="20" t="inlineStr"/>
       <c r="F140" s="20" t="inlineStr"/>
       <c r="G140" s="20" t="inlineStr"/>
-      <c r="H140" s="20" t="inlineStr"/>
+      <c r="H140" s="20" t="inlineStr">
+        <is>
+          <t>1,228</t>
+        </is>
+      </c>
       <c r="I140" s="20" t="inlineStr"/>
       <c r="J140" s="20" t="inlineStr"/>
-      <c r="K140" s="32" t="n"/>
-      <c r="L140" s="32" t="inlineStr"/>
+      <c r="K140" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L140" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M140" s="32" t="n"/>
       <c r="N140" s="32" t="n"/>
       <c r="O140" s="20" t="inlineStr"/>
@@ -7917,11 +8797,23 @@
       <c r="E141" s="20" t="inlineStr"/>
       <c r="F141" s="20" t="inlineStr"/>
       <c r="G141" s="20" t="inlineStr"/>
-      <c r="H141" s="20" t="inlineStr"/>
+      <c r="H141" s="20" t="inlineStr">
+        <is>
+          <t>5,793</t>
+        </is>
+      </c>
       <c r="I141" s="20" t="inlineStr"/>
       <c r="J141" s="20" t="inlineStr"/>
-      <c r="K141" s="32" t="n"/>
-      <c r="L141" s="32" t="inlineStr"/>
+      <c r="K141" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L141" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M141" s="32" t="n"/>
       <c r="N141" s="32" t="n"/>
       <c r="O141" s="20" t="inlineStr"/>
@@ -7960,11 +8852,23 @@
       <c r="E142" s="20" t="inlineStr"/>
       <c r="F142" s="20" t="inlineStr"/>
       <c r="G142" s="20" t="inlineStr"/>
-      <c r="H142" s="20" t="inlineStr"/>
+      <c r="H142" s="20" t="inlineStr">
+        <is>
+          <t>3,860</t>
+        </is>
+      </c>
       <c r="I142" s="20" t="inlineStr"/>
       <c r="J142" s="20" t="inlineStr"/>
-      <c r="K142" s="32" t="n"/>
-      <c r="L142" s="32" t="inlineStr"/>
+      <c r="K142" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L142" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M142" s="32" t="n"/>
       <c r="N142" s="32" t="n"/>
       <c r="O142" s="20" t="inlineStr"/>
@@ -8003,11 +8907,23 @@
       <c r="E143" s="20" t="inlineStr"/>
       <c r="F143" s="20" t="inlineStr"/>
       <c r="G143" s="20" t="inlineStr"/>
-      <c r="H143" s="20" t="inlineStr"/>
+      <c r="H143" s="20" t="inlineStr">
+        <is>
+          <t>3,925</t>
+        </is>
+      </c>
       <c r="I143" s="20" t="inlineStr"/>
       <c r="J143" s="20" t="inlineStr"/>
-      <c r="K143" s="32" t="n"/>
-      <c r="L143" s="32" t="inlineStr"/>
+      <c r="K143" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L143" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M143" s="32" t="n"/>
       <c r="N143" s="32" t="n"/>
       <c r="O143" s="20" t="inlineStr"/>
@@ -8046,11 +8962,23 @@
       <c r="E144" s="20" t="inlineStr"/>
       <c r="F144" s="20" t="inlineStr"/>
       <c r="G144" s="20" t="inlineStr"/>
-      <c r="H144" s="20" t="inlineStr"/>
+      <c r="H144" s="20" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
       <c r="I144" s="20" t="inlineStr"/>
       <c r="J144" s="20" t="inlineStr"/>
-      <c r="K144" s="32" t="n"/>
-      <c r="L144" s="32" t="inlineStr"/>
+      <c r="K144" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L144" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M144" s="32" t="n"/>
       <c r="N144" s="32" t="n"/>
       <c r="O144" s="20" t="inlineStr"/>
@@ -8089,11 +9017,23 @@
       <c r="E145" s="20" t="inlineStr"/>
       <c r="F145" s="20" t="inlineStr"/>
       <c r="G145" s="20" t="inlineStr"/>
-      <c r="H145" s="20" t="inlineStr"/>
+      <c r="H145" s="20" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
       <c r="I145" s="20" t="inlineStr"/>
       <c r="J145" s="20" t="inlineStr"/>
-      <c r="K145" s="32" t="n"/>
-      <c r="L145" s="32" t="inlineStr"/>
+      <c r="K145" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L145" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M145" s="32" t="n"/>
       <c r="N145" s="32" t="n"/>
       <c r="O145" s="20" t="inlineStr"/>
@@ -8132,11 +9072,23 @@
       <c r="E146" s="20" t="inlineStr"/>
       <c r="F146" s="20" t="inlineStr"/>
       <c r="G146" s="20" t="inlineStr"/>
-      <c r="H146" s="20" t="inlineStr"/>
+      <c r="H146" s="20" t="inlineStr">
+        <is>
+          <t>15,520</t>
+        </is>
+      </c>
       <c r="I146" s="20" t="inlineStr"/>
       <c r="J146" s="20" t="inlineStr"/>
-      <c r="K146" s="32" t="n"/>
-      <c r="L146" s="32" t="inlineStr"/>
+      <c r="K146" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L146" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M146" s="32" t="n"/>
       <c r="N146" s="32" t="n"/>
       <c r="O146" s="20" t="inlineStr"/>
@@ -8175,11 +9127,23 @@
       <c r="E147" s="20" t="inlineStr"/>
       <c r="F147" s="20" t="inlineStr"/>
       <c r="G147" s="20" t="inlineStr"/>
-      <c r="H147" s="20" t="inlineStr"/>
+      <c r="H147" s="20" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
       <c r="I147" s="20" t="inlineStr"/>
       <c r="J147" s="20" t="inlineStr"/>
-      <c r="K147" s="32" t="n"/>
-      <c r="L147" s="32" t="inlineStr"/>
+      <c r="K147" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L147" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M147" s="32" t="n"/>
       <c r="N147" s="32" t="n"/>
       <c r="O147" s="20" t="inlineStr"/>
@@ -8218,11 +9182,23 @@
       <c r="E148" s="20" t="inlineStr"/>
       <c r="F148" s="20" t="inlineStr"/>
       <c r="G148" s="20" t="inlineStr"/>
-      <c r="H148" s="20" t="inlineStr"/>
+      <c r="H148" s="20" t="inlineStr">
+        <is>
+          <t>4,030</t>
+        </is>
+      </c>
       <c r="I148" s="20" t="inlineStr"/>
       <c r="J148" s="20" t="inlineStr"/>
-      <c r="K148" s="32" t="n"/>
-      <c r="L148" s="32" t="inlineStr"/>
+      <c r="K148" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L148" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M148" s="32" t="n"/>
       <c r="N148" s="32" t="n"/>
       <c r="O148" s="20" t="inlineStr"/>
@@ -8261,11 +9237,23 @@
       <c r="E149" s="20" t="inlineStr"/>
       <c r="F149" s="20" t="inlineStr"/>
       <c r="G149" s="20" t="inlineStr"/>
-      <c r="H149" s="20" t="inlineStr"/>
+      <c r="H149" s="20" t="inlineStr">
+        <is>
+          <t>14,111</t>
+        </is>
+      </c>
       <c r="I149" s="20" t="inlineStr"/>
       <c r="J149" s="20" t="inlineStr"/>
-      <c r="K149" s="32" t="n"/>
-      <c r="L149" s="32" t="inlineStr"/>
+      <c r="K149" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L149" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M149" s="32" t="n"/>
       <c r="N149" s="32" t="n"/>
       <c r="O149" s="20" t="inlineStr"/>
@@ -8304,11 +9292,23 @@
       <c r="E150" s="20" t="inlineStr"/>
       <c r="F150" s="20" t="inlineStr"/>
       <c r="G150" s="20" t="inlineStr"/>
-      <c r="H150" s="20" t="inlineStr"/>
+      <c r="H150" s="20" t="inlineStr">
+        <is>
+          <t>3,160</t>
+        </is>
+      </c>
       <c r="I150" s="20" t="inlineStr"/>
       <c r="J150" s="20" t="inlineStr"/>
-      <c r="K150" s="32" t="n"/>
-      <c r="L150" s="32" t="inlineStr"/>
+      <c r="K150" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L150" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M150" s="32" t="n"/>
       <c r="N150" s="32" t="n"/>
       <c r="O150" s="20" t="inlineStr"/>
@@ -8347,11 +9347,23 @@
       <c r="E151" s="20" t="inlineStr"/>
       <c r="F151" s="20" t="inlineStr"/>
       <c r="G151" s="20" t="inlineStr"/>
-      <c r="H151" s="20" t="inlineStr"/>
+      <c r="H151" s="20" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
       <c r="I151" s="20" t="inlineStr"/>
       <c r="J151" s="20" t="inlineStr"/>
-      <c r="K151" s="32" t="n"/>
-      <c r="L151" s="32" t="inlineStr"/>
+      <c r="K151" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L151" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M151" s="32" t="n"/>
       <c r="N151" s="32" t="n"/>
       <c r="O151" s="20" t="inlineStr"/>
@@ -8390,11 +9402,23 @@
       <c r="E152" s="20" t="inlineStr"/>
       <c r="F152" s="20" t="inlineStr"/>
       <c r="G152" s="20" t="inlineStr"/>
-      <c r="H152" s="20" t="inlineStr"/>
+      <c r="H152" s="20" t="inlineStr">
+        <is>
+          <t>7,589</t>
+        </is>
+      </c>
       <c r="I152" s="20" t="inlineStr"/>
       <c r="J152" s="20" t="inlineStr"/>
-      <c r="K152" s="32" t="n"/>
-      <c r="L152" s="32" t="inlineStr"/>
+      <c r="K152" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L152" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M152" s="32" t="n"/>
       <c r="N152" s="32" t="n"/>
       <c r="O152" s="20" t="inlineStr"/>
@@ -8519,11 +9543,23 @@
       <c r="E155" s="20" t="inlineStr"/>
       <c r="F155" s="20" t="inlineStr"/>
       <c r="G155" s="20" t="inlineStr"/>
-      <c r="H155" s="20" t="inlineStr"/>
+      <c r="H155" s="20" t="inlineStr">
+        <is>
+          <t>3,523</t>
+        </is>
+      </c>
       <c r="I155" s="20" t="inlineStr"/>
       <c r="J155" s="20" t="inlineStr"/>
-      <c r="K155" s="32" t="n"/>
-      <c r="L155" s="32" t="inlineStr"/>
+      <c r="K155" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L155" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M155" s="32" t="n"/>
       <c r="N155" s="32" t="n"/>
       <c r="O155" s="20" t="inlineStr"/>
@@ -8562,11 +9598,23 @@
       <c r="E156" s="20" t="inlineStr"/>
       <c r="F156" s="20" t="inlineStr"/>
       <c r="G156" s="20" t="inlineStr"/>
-      <c r="H156" s="20" t="inlineStr"/>
+      <c r="H156" s="20" t="inlineStr">
+        <is>
+          <t>30,447</t>
+        </is>
+      </c>
       <c r="I156" s="20" t="inlineStr"/>
       <c r="J156" s="20" t="inlineStr"/>
-      <c r="K156" s="32" t="n"/>
-      <c r="L156" s="32" t="inlineStr"/>
+      <c r="K156" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L156" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M156" s="32" t="n"/>
       <c r="N156" s="32" t="n"/>
       <c r="O156" s="20" t="inlineStr"/>
@@ -8605,11 +9653,23 @@
       <c r="E157" s="20" t="inlineStr"/>
       <c r="F157" s="20" t="inlineStr"/>
       <c r="G157" s="20" t="inlineStr"/>
-      <c r="H157" s="20" t="inlineStr"/>
+      <c r="H157" s="20" t="inlineStr">
+        <is>
+          <t>18,067</t>
+        </is>
+      </c>
       <c r="I157" s="20" t="inlineStr"/>
       <c r="J157" s="20" t="inlineStr"/>
-      <c r="K157" s="32" t="n"/>
-      <c r="L157" s="32" t="inlineStr"/>
+      <c r="K157" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L157" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M157" s="32" t="n"/>
       <c r="N157" s="32" t="n"/>
       <c r="O157" s="20" t="inlineStr"/>
@@ -8648,11 +9708,23 @@
       <c r="E158" s="20" t="inlineStr"/>
       <c r="F158" s="20" t="inlineStr"/>
       <c r="G158" s="20" t="inlineStr"/>
-      <c r="H158" s="20" t="inlineStr"/>
+      <c r="H158" s="20" t="inlineStr">
+        <is>
+          <t>6,440</t>
+        </is>
+      </c>
       <c r="I158" s="20" t="inlineStr"/>
       <c r="J158" s="20" t="inlineStr"/>
-      <c r="K158" s="32" t="n"/>
-      <c r="L158" s="32" t="inlineStr"/>
+      <c r="K158" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L158" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M158" s="32" t="n"/>
       <c r="N158" s="32" t="n"/>
       <c r="O158" s="20" t="inlineStr"/>
@@ -8691,11 +9763,23 @@
       <c r="E159" s="20" t="inlineStr"/>
       <c r="F159" s="20" t="inlineStr"/>
       <c r="G159" s="20" t="inlineStr"/>
-      <c r="H159" s="20" t="inlineStr"/>
+      <c r="H159" s="20" t="inlineStr">
+        <is>
+          <t>61,876</t>
+        </is>
+      </c>
       <c r="I159" s="20" t="inlineStr"/>
       <c r="J159" s="20" t="inlineStr"/>
-      <c r="K159" s="32" t="n"/>
-      <c r="L159" s="32" t="inlineStr"/>
+      <c r="K159" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L159" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M159" s="32" t="n"/>
       <c r="N159" s="32" t="n"/>
       <c r="O159" s="20" t="inlineStr"/>
@@ -8734,11 +9818,23 @@
       <c r="E160" s="20" t="inlineStr"/>
       <c r="F160" s="20" t="inlineStr"/>
       <c r="G160" s="20" t="inlineStr"/>
-      <c r="H160" s="20" t="inlineStr"/>
+      <c r="H160" s="20" t="inlineStr">
+        <is>
+          <t>3,542</t>
+        </is>
+      </c>
       <c r="I160" s="20" t="inlineStr"/>
       <c r="J160" s="20" t="inlineStr"/>
-      <c r="K160" s="32" t="n"/>
-      <c r="L160" s="32" t="inlineStr"/>
+      <c r="K160" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L160" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M160" s="32" t="n"/>
       <c r="N160" s="32" t="n"/>
       <c r="O160" s="20" t="inlineStr"/>
@@ -8777,11 +9873,23 @@
       <c r="E161" s="20" t="inlineStr"/>
       <c r="F161" s="20" t="inlineStr"/>
       <c r="G161" s="20" t="inlineStr"/>
-      <c r="H161" s="20" t="inlineStr"/>
+      <c r="H161" s="20" t="inlineStr">
+        <is>
+          <t>8,135</t>
+        </is>
+      </c>
       <c r="I161" s="20" t="inlineStr"/>
       <c r="J161" s="20" t="inlineStr"/>
-      <c r="K161" s="32" t="n"/>
-      <c r="L161" s="32" t="inlineStr"/>
+      <c r="K161" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L161" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M161" s="32" t="n"/>
       <c r="N161" s="32" t="n"/>
       <c r="O161" s="20" t="inlineStr"/>
@@ -8820,11 +9928,23 @@
       <c r="E162" s="20" t="inlineStr"/>
       <c r="F162" s="20" t="inlineStr"/>
       <c r="G162" s="20" t="inlineStr"/>
-      <c r="H162" s="20" t="inlineStr"/>
+      <c r="H162" s="20" t="inlineStr">
+        <is>
+          <t>2,343</t>
+        </is>
+      </c>
       <c r="I162" s="20" t="inlineStr"/>
       <c r="J162" s="20" t="inlineStr"/>
-      <c r="K162" s="32" t="n"/>
-      <c r="L162" s="32" t="inlineStr"/>
+      <c r="K162" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L162" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M162" s="32" t="n"/>
       <c r="N162" s="32" t="n"/>
       <c r="O162" s="20" t="inlineStr"/>
@@ -8906,11 +10026,23 @@
       <c r="E164" s="20" t="inlineStr"/>
       <c r="F164" s="20" t="inlineStr"/>
       <c r="G164" s="20" t="inlineStr"/>
-      <c r="H164" s="20" t="inlineStr"/>
+      <c r="H164" s="20" t="inlineStr">
+        <is>
+          <t>16,500</t>
+        </is>
+      </c>
       <c r="I164" s="20" t="inlineStr"/>
       <c r="J164" s="20" t="inlineStr"/>
-      <c r="K164" s="32" t="n"/>
-      <c r="L164" s="32" t="inlineStr"/>
+      <c r="K164" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L164" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M164" s="32" t="n"/>
       <c r="N164" s="32" t="n"/>
       <c r="O164" s="20" t="inlineStr"/>
@@ -9035,11 +10167,23 @@
       <c r="E167" s="20" t="inlineStr"/>
       <c r="F167" s="20" t="inlineStr"/>
       <c r="G167" s="20" t="inlineStr"/>
-      <c r="H167" s="20" t="inlineStr"/>
+      <c r="H167" s="20" t="inlineStr">
+        <is>
+          <t>3,204</t>
+        </is>
+      </c>
       <c r="I167" s="20" t="inlineStr"/>
       <c r="J167" s="20" t="inlineStr"/>
-      <c r="K167" s="32" t="n"/>
-      <c r="L167" s="32" t="inlineStr"/>
+      <c r="K167" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L167" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M167" s="32" t="n"/>
       <c r="N167" s="32" t="n"/>
       <c r="O167" s="20" t="inlineStr"/>
@@ -9078,11 +10222,23 @@
       <c r="E168" s="20" t="inlineStr"/>
       <c r="F168" s="20" t="inlineStr"/>
       <c r="G168" s="20" t="inlineStr"/>
-      <c r="H168" s="20" t="inlineStr"/>
+      <c r="H168" s="20" t="inlineStr">
+        <is>
+          <t>16,127</t>
+        </is>
+      </c>
       <c r="I168" s="20" t="inlineStr"/>
       <c r="J168" s="20" t="inlineStr"/>
-      <c r="K168" s="32" t="n"/>
-      <c r="L168" s="32" t="inlineStr"/>
+      <c r="K168" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L168" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M168" s="32" t="n"/>
       <c r="N168" s="32" t="n"/>
       <c r="O168" s="20" t="inlineStr"/>
@@ -9121,11 +10277,23 @@
       <c r="E169" s="20" t="inlineStr"/>
       <c r="F169" s="20" t="inlineStr"/>
       <c r="G169" s="20" t="inlineStr"/>
-      <c r="H169" s="20" t="inlineStr"/>
+      <c r="H169" s="20" t="inlineStr">
+        <is>
+          <t>3,260</t>
+        </is>
+      </c>
       <c r="I169" s="20" t="inlineStr"/>
       <c r="J169" s="20" t="inlineStr"/>
-      <c r="K169" s="32" t="n"/>
-      <c r="L169" s="32" t="inlineStr"/>
+      <c r="K169" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L169" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M169" s="32" t="n"/>
       <c r="N169" s="32" t="n"/>
       <c r="O169" s="20" t="inlineStr"/>
@@ -9164,11 +10332,23 @@
       <c r="E170" s="20" t="inlineStr"/>
       <c r="F170" s="20" t="inlineStr"/>
       <c r="G170" s="20" t="inlineStr"/>
-      <c r="H170" s="20" t="inlineStr"/>
+      <c r="H170" s="20" t="inlineStr">
+        <is>
+          <t>4,364</t>
+        </is>
+      </c>
       <c r="I170" s="20" t="inlineStr"/>
       <c r="J170" s="20" t="inlineStr"/>
-      <c r="K170" s="32" t="n"/>
-      <c r="L170" s="32" t="inlineStr"/>
+      <c r="K170" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L170" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M170" s="32" t="n"/>
       <c r="N170" s="32" t="n"/>
       <c r="O170" s="20" t="inlineStr"/>
@@ -9250,11 +10430,23 @@
       <c r="E172" s="20" t="inlineStr"/>
       <c r="F172" s="20" t="inlineStr"/>
       <c r="G172" s="20" t="inlineStr"/>
-      <c r="H172" s="20" t="inlineStr"/>
+      <c r="H172" s="20" t="inlineStr">
+        <is>
+          <t>2,085</t>
+        </is>
+      </c>
       <c r="I172" s="20" t="inlineStr"/>
       <c r="J172" s="20" t="inlineStr"/>
-      <c r="K172" s="32" t="n"/>
-      <c r="L172" s="32" t="inlineStr"/>
+      <c r="K172" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L172" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M172" s="32" t="n"/>
       <c r="N172" s="32" t="n"/>
       <c r="O172" s="20" t="inlineStr"/>
@@ -9293,11 +10485,23 @@
       <c r="E173" s="20" t="inlineStr"/>
       <c r="F173" s="20" t="inlineStr"/>
       <c r="G173" s="20" t="inlineStr"/>
-      <c r="H173" s="20" t="inlineStr"/>
+      <c r="H173" s="20" t="inlineStr">
+        <is>
+          <t>13,618</t>
+        </is>
+      </c>
       <c r="I173" s="20" t="inlineStr"/>
       <c r="J173" s="20" t="inlineStr"/>
-      <c r="K173" s="32" t="n"/>
-      <c r="L173" s="32" t="inlineStr"/>
+      <c r="K173" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L173" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M173" s="32" t="n"/>
       <c r="N173" s="32" t="n"/>
       <c r="O173" s="20" t="inlineStr"/>
@@ -9336,11 +10540,23 @@
       <c r="E174" s="20" t="inlineStr"/>
       <c r="F174" s="20" t="inlineStr"/>
       <c r="G174" s="20" t="inlineStr"/>
-      <c r="H174" s="20" t="inlineStr"/>
+      <c r="H174" s="20" t="inlineStr">
+        <is>
+          <t>6,780</t>
+        </is>
+      </c>
       <c r="I174" s="20" t="inlineStr"/>
       <c r="J174" s="20" t="inlineStr"/>
-      <c r="K174" s="32" t="n"/>
-      <c r="L174" s="32" t="inlineStr"/>
+      <c r="K174" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L174" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M174" s="32" t="n"/>
       <c r="N174" s="32" t="n"/>
       <c r="O174" s="20" t="inlineStr"/>
@@ -9379,11 +10595,23 @@
       <c r="E175" s="20" t="inlineStr"/>
       <c r="F175" s="20" t="inlineStr"/>
       <c r="G175" s="20" t="inlineStr"/>
-      <c r="H175" s="20" t="inlineStr"/>
+      <c r="H175" s="20" t="inlineStr">
+        <is>
+          <t>8,986</t>
+        </is>
+      </c>
       <c r="I175" s="20" t="inlineStr"/>
       <c r="J175" s="20" t="inlineStr"/>
-      <c r="K175" s="32" t="n"/>
-      <c r="L175" s="32" t="inlineStr"/>
+      <c r="K175" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L175" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M175" s="32" t="n"/>
       <c r="N175" s="32" t="n"/>
       <c r="O175" s="20" t="inlineStr"/>
@@ -9422,11 +10650,23 @@
       <c r="E176" s="20" t="inlineStr"/>
       <c r="F176" s="20" t="inlineStr"/>
       <c r="G176" s="20" t="inlineStr"/>
-      <c r="H176" s="20" t="inlineStr"/>
+      <c r="H176" s="20" t="inlineStr">
+        <is>
+          <t>7,321</t>
+        </is>
+      </c>
       <c r="I176" s="20" t="inlineStr"/>
       <c r="J176" s="20" t="inlineStr"/>
-      <c r="K176" s="32" t="n"/>
-      <c r="L176" s="32" t="inlineStr"/>
+      <c r="K176" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L176" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M176" s="32" t="n"/>
       <c r="N176" s="32" t="n"/>
       <c r="O176" s="20" t="inlineStr"/>
@@ -9465,11 +10705,23 @@
       <c r="E177" s="20" t="inlineStr"/>
       <c r="F177" s="20" t="inlineStr"/>
       <c r="G177" s="20" t="inlineStr"/>
-      <c r="H177" s="20" t="inlineStr"/>
+      <c r="H177" s="20" t="inlineStr">
+        <is>
+          <t>14,593</t>
+        </is>
+      </c>
       <c r="I177" s="20" t="inlineStr"/>
       <c r="J177" s="20" t="inlineStr"/>
-      <c r="K177" s="32" t="n"/>
-      <c r="L177" s="32" t="inlineStr"/>
+      <c r="K177" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L177" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M177" s="32" t="n"/>
       <c r="N177" s="32" t="n"/>
       <c r="O177" s="20" t="inlineStr"/>
@@ -9508,11 +10760,23 @@
       <c r="E178" s="20" t="inlineStr"/>
       <c r="F178" s="20" t="inlineStr"/>
       <c r="G178" s="20" t="inlineStr"/>
-      <c r="H178" s="20" t="inlineStr"/>
+      <c r="H178" s="20" t="inlineStr">
+        <is>
+          <t>6,265</t>
+        </is>
+      </c>
       <c r="I178" s="20" t="inlineStr"/>
       <c r="J178" s="20" t="inlineStr"/>
-      <c r="K178" s="32" t="n"/>
-      <c r="L178" s="32" t="inlineStr"/>
+      <c r="K178" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L178" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M178" s="32" t="n"/>
       <c r="N178" s="32" t="n"/>
       <c r="O178" s="20" t="inlineStr"/>
@@ -9551,11 +10815,23 @@
       <c r="E179" s="20" t="inlineStr"/>
       <c r="F179" s="20" t="inlineStr"/>
       <c r="G179" s="20" t="inlineStr"/>
-      <c r="H179" s="20" t="inlineStr"/>
+      <c r="H179" s="20" t="inlineStr">
+        <is>
+          <t>8,921</t>
+        </is>
+      </c>
       <c r="I179" s="20" t="inlineStr"/>
       <c r="J179" s="20" t="inlineStr"/>
-      <c r="K179" s="32" t="n"/>
-      <c r="L179" s="32" t="inlineStr"/>
+      <c r="K179" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L179" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M179" s="32" t="n"/>
       <c r="N179" s="32" t="n"/>
       <c r="O179" s="20" t="inlineStr"/>
@@ -9594,11 +10870,23 @@
       <c r="E180" s="20" t="inlineStr"/>
       <c r="F180" s="20" t="inlineStr"/>
       <c r="G180" s="20" t="inlineStr"/>
-      <c r="H180" s="20" t="inlineStr"/>
+      <c r="H180" s="20" t="inlineStr">
+        <is>
+          <t>6,631</t>
+        </is>
+      </c>
       <c r="I180" s="20" t="inlineStr"/>
       <c r="J180" s="20" t="inlineStr"/>
-      <c r="K180" s="32" t="n"/>
-      <c r="L180" s="32" t="inlineStr"/>
+      <c r="K180" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L180" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M180" s="32" t="n"/>
       <c r="N180" s="32" t="n"/>
       <c r="O180" s="20" t="inlineStr"/>
@@ -9637,11 +10925,23 @@
       <c r="E181" s="20" t="inlineStr"/>
       <c r="F181" s="20" t="inlineStr"/>
       <c r="G181" s="20" t="inlineStr"/>
-      <c r="H181" s="20" t="inlineStr"/>
+      <c r="H181" s="20" t="inlineStr">
+        <is>
+          <t>14,766</t>
+        </is>
+      </c>
       <c r="I181" s="20" t="inlineStr"/>
       <c r="J181" s="20" t="inlineStr"/>
-      <c r="K181" s="32" t="n"/>
-      <c r="L181" s="32" t="inlineStr"/>
+      <c r="K181" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L181" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M181" s="32" t="n"/>
       <c r="N181" s="32" t="n"/>
       <c r="O181" s="20" t="inlineStr"/>
@@ -9680,11 +10980,23 @@
       <c r="E182" s="20" t="inlineStr"/>
       <c r="F182" s="20" t="inlineStr"/>
       <c r="G182" s="20" t="inlineStr"/>
-      <c r="H182" s="20" t="inlineStr"/>
+      <c r="H182" s="20" t="inlineStr">
+        <is>
+          <t>41,574</t>
+        </is>
+      </c>
       <c r="I182" s="20" t="inlineStr"/>
       <c r="J182" s="20" t="inlineStr"/>
-      <c r="K182" s="32" t="n"/>
-      <c r="L182" s="32" t="inlineStr"/>
+      <c r="K182" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L182" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M182" s="32" t="n"/>
       <c r="N182" s="32" t="n"/>
       <c r="O182" s="20" t="inlineStr"/>
@@ -9723,11 +11035,23 @@
       <c r="E183" s="20" t="inlineStr"/>
       <c r="F183" s="20" t="inlineStr"/>
       <c r="G183" s="20" t="inlineStr"/>
-      <c r="H183" s="20" t="inlineStr"/>
+      <c r="H183" s="20" t="inlineStr">
+        <is>
+          <t>11,522</t>
+        </is>
+      </c>
       <c r="I183" s="20" t="inlineStr"/>
       <c r="J183" s="20" t="inlineStr"/>
-      <c r="K183" s="32" t="n"/>
-      <c r="L183" s="32" t="inlineStr"/>
+      <c r="K183" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L183" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M183" s="32" t="n"/>
       <c r="N183" s="32" t="n"/>
       <c r="O183" s="20" t="inlineStr"/>
@@ -9852,11 +11176,23 @@
       <c r="E186" s="20" t="inlineStr"/>
       <c r="F186" s="20" t="inlineStr"/>
       <c r="G186" s="20" t="inlineStr"/>
-      <c r="H186" s="20" t="inlineStr"/>
+      <c r="H186" s="20" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
       <c r="I186" s="20" t="inlineStr"/>
       <c r="J186" s="20" t="inlineStr"/>
-      <c r="K186" s="32" t="n"/>
-      <c r="L186" s="32" t="inlineStr"/>
+      <c r="K186" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L186" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M186" s="32" t="n"/>
       <c r="N186" s="32" t="n"/>
       <c r="O186" s="20" t="inlineStr"/>
@@ -9895,11 +11231,23 @@
       <c r="E187" s="20" t="inlineStr"/>
       <c r="F187" s="20" t="inlineStr"/>
       <c r="G187" s="20" t="inlineStr"/>
-      <c r="H187" s="20" t="inlineStr"/>
+      <c r="H187" s="20" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
       <c r="I187" s="20" t="inlineStr"/>
       <c r="J187" s="20" t="inlineStr"/>
-      <c r="K187" s="32" t="n"/>
-      <c r="L187" s="32" t="inlineStr"/>
+      <c r="K187" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L187" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M187" s="32" t="n"/>
       <c r="N187" s="32" t="n"/>
       <c r="O187" s="20" t="inlineStr"/>
@@ -9938,11 +11286,23 @@
       <c r="E188" s="20" t="inlineStr"/>
       <c r="F188" s="20" t="inlineStr"/>
       <c r="G188" s="20" t="inlineStr"/>
-      <c r="H188" s="20" t="inlineStr"/>
+      <c r="H188" s="20" t="inlineStr">
+        <is>
+          <t>6,349</t>
+        </is>
+      </c>
       <c r="I188" s="20" t="inlineStr"/>
       <c r="J188" s="20" t="inlineStr"/>
-      <c r="K188" s="32" t="n"/>
-      <c r="L188" s="32" t="inlineStr"/>
+      <c r="K188" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L188" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M188" s="32" t="n"/>
       <c r="N188" s="32" t="n"/>
       <c r="O188" s="20" t="inlineStr"/>
@@ -9981,11 +11341,23 @@
       <c r="E189" s="20" t="inlineStr"/>
       <c r="F189" s="20" t="inlineStr"/>
       <c r="G189" s="20" t="inlineStr"/>
-      <c r="H189" s="20" t="inlineStr"/>
+      <c r="H189" s="20" t="inlineStr">
+        <is>
+          <t>27,974</t>
+        </is>
+      </c>
       <c r="I189" s="20" t="inlineStr"/>
       <c r="J189" s="20" t="inlineStr"/>
-      <c r="K189" s="32" t="n"/>
-      <c r="L189" s="32" t="inlineStr"/>
+      <c r="K189" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L189" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M189" s="32" t="n"/>
       <c r="N189" s="32" t="n"/>
       <c r="O189" s="20" t="inlineStr"/>
@@ -10024,11 +11396,23 @@
       <c r="E190" s="20" t="inlineStr"/>
       <c r="F190" s="20" t="inlineStr"/>
       <c r="G190" s="20" t="inlineStr"/>
-      <c r="H190" s="20" t="inlineStr"/>
+      <c r="H190" s="20" t="inlineStr">
+        <is>
+          <t>1,724</t>
+        </is>
+      </c>
       <c r="I190" s="20" t="inlineStr"/>
       <c r="J190" s="20" t="inlineStr"/>
-      <c r="K190" s="32" t="n"/>
-      <c r="L190" s="32" t="inlineStr"/>
+      <c r="K190" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L190" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M190" s="32" t="n"/>
       <c r="N190" s="32" t="n"/>
       <c r="O190" s="20" t="inlineStr"/>
@@ -10067,11 +11451,23 @@
       <c r="E191" s="20" t="inlineStr"/>
       <c r="F191" s="20" t="inlineStr"/>
       <c r="G191" s="20" t="inlineStr"/>
-      <c r="H191" s="20" t="inlineStr"/>
+      <c r="H191" s="20" t="inlineStr">
+        <is>
+          <t>10,183</t>
+        </is>
+      </c>
       <c r="I191" s="20" t="inlineStr"/>
       <c r="J191" s="20" t="inlineStr"/>
-      <c r="K191" s="32" t="n"/>
-      <c r="L191" s="32" t="inlineStr"/>
+      <c r="K191" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L191" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M191" s="32" t="n"/>
       <c r="N191" s="32" t="n"/>
       <c r="O191" s="20" t="inlineStr"/>
@@ -10110,11 +11506,23 @@
       <c r="E192" s="20" t="inlineStr"/>
       <c r="F192" s="20" t="inlineStr"/>
       <c r="G192" s="20" t="inlineStr"/>
-      <c r="H192" s="20" t="inlineStr"/>
+      <c r="H192" s="20" t="inlineStr">
+        <is>
+          <t>1,576</t>
+        </is>
+      </c>
       <c r="I192" s="20" t="inlineStr"/>
       <c r="J192" s="20" t="inlineStr"/>
-      <c r="K192" s="32" t="n"/>
-      <c r="L192" s="32" t="inlineStr"/>
+      <c r="K192" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L192" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M192" s="32" t="n"/>
       <c r="N192" s="32" t="n"/>
       <c r="O192" s="20" t="inlineStr"/>
@@ -10153,11 +11561,23 @@
       <c r="E193" s="20" t="inlineStr"/>
       <c r="F193" s="20" t="inlineStr"/>
       <c r="G193" s="20" t="inlineStr"/>
-      <c r="H193" s="20" t="inlineStr"/>
+      <c r="H193" s="20" t="inlineStr">
+        <is>
+          <t>1,962</t>
+        </is>
+      </c>
       <c r="I193" s="20" t="inlineStr"/>
       <c r="J193" s="20" t="inlineStr"/>
-      <c r="K193" s="32" t="n"/>
-      <c r="L193" s="32" t="inlineStr"/>
+      <c r="K193" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L193" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M193" s="32" t="n"/>
       <c r="N193" s="32" t="n"/>
       <c r="O193" s="20" t="inlineStr"/>
@@ -10196,11 +11616,23 @@
       <c r="E194" s="20" t="inlineStr"/>
       <c r="F194" s="20" t="inlineStr"/>
       <c r="G194" s="20" t="inlineStr"/>
-      <c r="H194" s="20" t="inlineStr"/>
+      <c r="H194" s="20" t="inlineStr">
+        <is>
+          <t>3,606</t>
+        </is>
+      </c>
       <c r="I194" s="20" t="inlineStr"/>
       <c r="J194" s="20" t="inlineStr"/>
-      <c r="K194" s="32" t="n"/>
-      <c r="L194" s="32" t="inlineStr"/>
+      <c r="K194" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L194" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M194" s="32" t="n"/>
       <c r="N194" s="32" t="n"/>
       <c r="O194" s="20" t="inlineStr"/>
@@ -10239,11 +11671,23 @@
       <c r="E195" s="20" t="inlineStr"/>
       <c r="F195" s="20" t="inlineStr"/>
       <c r="G195" s="20" t="inlineStr"/>
-      <c r="H195" s="20" t="inlineStr"/>
+      <c r="H195" s="20" t="inlineStr">
+        <is>
+          <t>5,146</t>
+        </is>
+      </c>
       <c r="I195" s="20" t="inlineStr"/>
       <c r="J195" s="20" t="inlineStr"/>
-      <c r="K195" s="32" t="n"/>
-      <c r="L195" s="32" t="inlineStr"/>
+      <c r="K195" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L195" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M195" s="32" t="n"/>
       <c r="N195" s="32" t="n"/>
       <c r="O195" s="20" t="inlineStr"/>
@@ -10282,11 +11726,23 @@
       <c r="E196" s="20" t="inlineStr"/>
       <c r="F196" s="20" t="inlineStr"/>
       <c r="G196" s="20" t="inlineStr"/>
-      <c r="H196" s="20" t="inlineStr"/>
+      <c r="H196" s="20" t="inlineStr">
+        <is>
+          <t>14,567</t>
+        </is>
+      </c>
       <c r="I196" s="20" t="inlineStr"/>
       <c r="J196" s="20" t="inlineStr"/>
-      <c r="K196" s="32" t="n"/>
-      <c r="L196" s="32" t="inlineStr"/>
+      <c r="K196" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L196" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M196" s="32" t="n"/>
       <c r="N196" s="32" t="n"/>
       <c r="O196" s="20" t="inlineStr"/>
@@ -10325,11 +11781,23 @@
       <c r="E197" s="20" t="inlineStr"/>
       <c r="F197" s="20" t="inlineStr"/>
       <c r="G197" s="20" t="inlineStr"/>
-      <c r="H197" s="20" t="inlineStr"/>
+      <c r="H197" s="20" t="inlineStr">
+        <is>
+          <t>6,156</t>
+        </is>
+      </c>
       <c r="I197" s="20" t="inlineStr"/>
       <c r="J197" s="20" t="inlineStr"/>
-      <c r="K197" s="32" t="n"/>
-      <c r="L197" s="32" t="inlineStr"/>
+      <c r="K197" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L197" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M197" s="32" t="n"/>
       <c r="N197" s="32" t="n"/>
       <c r="O197" s="20" t="inlineStr"/>
@@ -10368,11 +11836,23 @@
       <c r="E198" s="20" t="inlineStr"/>
       <c r="F198" s="20" t="inlineStr"/>
       <c r="G198" s="20" t="inlineStr"/>
-      <c r="H198" s="20" t="inlineStr"/>
+      <c r="H198" s="20" t="inlineStr">
+        <is>
+          <t>16,592</t>
+        </is>
+      </c>
       <c r="I198" s="20" t="inlineStr"/>
       <c r="J198" s="20" t="inlineStr"/>
-      <c r="K198" s="32" t="n"/>
-      <c r="L198" s="32" t="inlineStr"/>
+      <c r="K198" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L198" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M198" s="32" t="n"/>
       <c r="N198" s="32" t="n"/>
       <c r="O198" s="20" t="inlineStr"/>
@@ -10411,11 +11891,23 @@
       <c r="E199" s="20" t="inlineStr"/>
       <c r="F199" s="20" t="inlineStr"/>
       <c r="G199" s="20" t="inlineStr"/>
-      <c r="H199" s="20" t="inlineStr"/>
+      <c r="H199" s="20" t="inlineStr">
+        <is>
+          <t>2,869</t>
+        </is>
+      </c>
       <c r="I199" s="20" t="inlineStr"/>
       <c r="J199" s="20" t="inlineStr"/>
-      <c r="K199" s="32" t="n"/>
-      <c r="L199" s="32" t="inlineStr"/>
+      <c r="K199" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L199" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M199" s="32" t="n"/>
       <c r="N199" s="32" t="n"/>
       <c r="O199" s="20" t="inlineStr"/>
@@ -10497,11 +11989,23 @@
       <c r="E201" s="20" t="inlineStr"/>
       <c r="F201" s="20" t="inlineStr"/>
       <c r="G201" s="20" t="inlineStr"/>
-      <c r="H201" s="20" t="inlineStr"/>
+      <c r="H201" s="20" t="inlineStr">
+        <is>
+          <t>28,295</t>
+        </is>
+      </c>
       <c r="I201" s="20" t="inlineStr"/>
       <c r="J201" s="20" t="inlineStr"/>
-      <c r="K201" s="32" t="n"/>
-      <c r="L201" s="32" t="inlineStr"/>
+      <c r="K201" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L201" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M201" s="32" t="n"/>
       <c r="N201" s="32" t="n"/>
       <c r="O201" s="20" t="inlineStr"/>
@@ -10540,11 +12044,23 @@
       <c r="E202" s="20" t="inlineStr"/>
       <c r="F202" s="20" t="inlineStr"/>
       <c r="G202" s="20" t="inlineStr"/>
-      <c r="H202" s="20" t="inlineStr"/>
+      <c r="H202" s="20" t="inlineStr">
+        <is>
+          <t>58,084</t>
+        </is>
+      </c>
       <c r="I202" s="20" t="inlineStr"/>
       <c r="J202" s="20" t="inlineStr"/>
-      <c r="K202" s="32" t="n"/>
-      <c r="L202" s="32" t="inlineStr"/>
+      <c r="K202" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L202" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M202" s="32" t="n"/>
       <c r="N202" s="32" t="n"/>
       <c r="O202" s="20" t="inlineStr"/>
@@ -10583,11 +12099,23 @@
       <c r="E203" s="20" t="inlineStr"/>
       <c r="F203" s="20" t="inlineStr"/>
       <c r="G203" s="20" t="inlineStr"/>
-      <c r="H203" s="20" t="inlineStr"/>
+      <c r="H203" s="20" t="inlineStr">
+        <is>
+          <t>41,477</t>
+        </is>
+      </c>
       <c r="I203" s="20" t="inlineStr"/>
       <c r="J203" s="20" t="inlineStr"/>
-      <c r="K203" s="32" t="n"/>
-      <c r="L203" s="32" t="inlineStr"/>
+      <c r="K203" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L203" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M203" s="32" t="n"/>
       <c r="N203" s="32" t="n"/>
       <c r="O203" s="20" t="inlineStr"/>
@@ -10626,11 +12154,23 @@
       <c r="E204" s="20" t="inlineStr"/>
       <c r="F204" s="20" t="inlineStr"/>
       <c r="G204" s="20" t="inlineStr"/>
-      <c r="H204" s="20" t="inlineStr"/>
+      <c r="H204" s="20" t="inlineStr">
+        <is>
+          <t>10,600</t>
+        </is>
+      </c>
       <c r="I204" s="20" t="inlineStr"/>
       <c r="J204" s="20" t="inlineStr"/>
-      <c r="K204" s="32" t="n"/>
-      <c r="L204" s="32" t="inlineStr"/>
+      <c r="K204" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L204" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M204" s="32" t="n"/>
       <c r="N204" s="32" t="n"/>
       <c r="O204" s="20" t="inlineStr"/>
@@ -10669,11 +12209,23 @@
       <c r="E205" s="20" t="inlineStr"/>
       <c r="F205" s="20" t="inlineStr"/>
       <c r="G205" s="20" t="inlineStr"/>
-      <c r="H205" s="20" t="inlineStr"/>
+      <c r="H205" s="20" t="inlineStr">
+        <is>
+          <t>58,220</t>
+        </is>
+      </c>
       <c r="I205" s="20" t="inlineStr"/>
       <c r="J205" s="20" t="inlineStr"/>
-      <c r="K205" s="32" t="n"/>
-      <c r="L205" s="32" t="inlineStr"/>
+      <c r="K205" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L205" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M205" s="32" t="n"/>
       <c r="N205" s="32" t="n"/>
       <c r="O205" s="20" t="inlineStr"/>
@@ -10712,11 +12264,23 @@
       <c r="E206" s="20" t="inlineStr"/>
       <c r="F206" s="20" t="inlineStr"/>
       <c r="G206" s="20" t="inlineStr"/>
-      <c r="H206" s="20" t="inlineStr"/>
+      <c r="H206" s="20" t="inlineStr">
+        <is>
+          <t>1,207</t>
+        </is>
+      </c>
       <c r="I206" s="20" t="inlineStr"/>
       <c r="J206" s="20" t="inlineStr"/>
-      <c r="K206" s="32" t="n"/>
-      <c r="L206" s="32" t="inlineStr"/>
+      <c r="K206" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L206" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M206" s="32" t="n"/>
       <c r="N206" s="32" t="n"/>
       <c r="O206" s="20" t="inlineStr"/>
@@ -10755,11 +12319,23 @@
       <c r="E207" s="20" t="inlineStr"/>
       <c r="F207" s="20" t="inlineStr"/>
       <c r="G207" s="20" t="inlineStr"/>
-      <c r="H207" s="20" t="inlineStr"/>
+      <c r="H207" s="20" t="inlineStr">
+        <is>
+          <t>2,425</t>
+        </is>
+      </c>
       <c r="I207" s="20" t="inlineStr"/>
       <c r="J207" s="20" t="inlineStr"/>
-      <c r="K207" s="32" t="n"/>
-      <c r="L207" s="32" t="inlineStr"/>
+      <c r="K207" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L207" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M207" s="32" t="n"/>
       <c r="N207" s="32" t="n"/>
       <c r="O207" s="20" t="inlineStr"/>
@@ -10798,11 +12374,23 @@
       <c r="E208" s="20" t="inlineStr"/>
       <c r="F208" s="20" t="inlineStr"/>
       <c r="G208" s="20" t="inlineStr"/>
-      <c r="H208" s="20" t="inlineStr"/>
+      <c r="H208" s="20" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
       <c r="I208" s="20" t="inlineStr"/>
       <c r="J208" s="20" t="inlineStr"/>
-      <c r="K208" s="32" t="n"/>
-      <c r="L208" s="32" t="inlineStr"/>
+      <c r="K208" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L208" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M208" s="32" t="n"/>
       <c r="N208" s="32" t="n"/>
       <c r="O208" s="20" t="inlineStr"/>
@@ -10841,11 +12429,23 @@
       <c r="E209" s="20" t="inlineStr"/>
       <c r="F209" s="20" t="inlineStr"/>
       <c r="G209" s="20" t="inlineStr"/>
-      <c r="H209" s="20" t="inlineStr"/>
+      <c r="H209" s="20" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="I209" s="20" t="inlineStr"/>
       <c r="J209" s="20" t="inlineStr"/>
-      <c r="K209" s="32" t="n"/>
-      <c r="L209" s="32" t="inlineStr"/>
+      <c r="K209" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L209" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M209" s="32" t="n"/>
       <c r="N209" s="32" t="n"/>
       <c r="O209" s="20" t="inlineStr"/>
@@ -10884,11 +12484,23 @@
       <c r="E210" s="20" t="inlineStr"/>
       <c r="F210" s="20" t="inlineStr"/>
       <c r="G210" s="20" t="inlineStr"/>
-      <c r="H210" s="20" t="inlineStr"/>
+      <c r="H210" s="20" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
       <c r="I210" s="20" t="inlineStr"/>
       <c r="J210" s="20" t="inlineStr"/>
-      <c r="K210" s="32" t="n"/>
-      <c r="L210" s="32" t="inlineStr"/>
+      <c r="K210" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L210" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M210" s="32" t="n"/>
       <c r="N210" s="32" t="n"/>
       <c r="O210" s="20" t="inlineStr"/>
@@ -10970,11 +12582,23 @@
       <c r="E212" s="20" t="inlineStr"/>
       <c r="F212" s="20" t="inlineStr"/>
       <c r="G212" s="20" t="inlineStr"/>
-      <c r="H212" s="20" t="inlineStr"/>
+      <c r="H212" s="20" t="inlineStr">
+        <is>
+          <t>9,952</t>
+        </is>
+      </c>
       <c r="I212" s="20" t="inlineStr"/>
       <c r="J212" s="20" t="inlineStr"/>
-      <c r="K212" s="32" t="n"/>
-      <c r="L212" s="32" t="inlineStr"/>
+      <c r="K212" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L212" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M212" s="32" t="n"/>
       <c r="N212" s="32" t="n"/>
       <c r="O212" s="20" t="inlineStr"/>
@@ -11013,11 +12637,23 @@
       <c r="E213" s="20" t="inlineStr"/>
       <c r="F213" s="20" t="inlineStr"/>
       <c r="G213" s="20" t="inlineStr"/>
-      <c r="H213" s="20" t="inlineStr"/>
+      <c r="H213" s="20" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
       <c r="I213" s="20" t="inlineStr"/>
       <c r="J213" s="20" t="inlineStr"/>
-      <c r="K213" s="32" t="n"/>
-      <c r="L213" s="32" t="inlineStr"/>
+      <c r="K213" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L213" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M213" s="32" t="n"/>
       <c r="N213" s="32" t="n"/>
       <c r="O213" s="20" t="inlineStr"/>
@@ -11099,11 +12735,23 @@
       <c r="E215" s="20" t="inlineStr"/>
       <c r="F215" s="20" t="inlineStr"/>
       <c r="G215" s="20" t="inlineStr"/>
-      <c r="H215" s="20" t="inlineStr"/>
+      <c r="H215" s="20" t="inlineStr">
+        <is>
+          <t>7,363</t>
+        </is>
+      </c>
       <c r="I215" s="20" t="inlineStr"/>
       <c r="J215" s="20" t="inlineStr"/>
-      <c r="K215" s="32" t="n"/>
-      <c r="L215" s="32" t="inlineStr"/>
+      <c r="K215" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L215" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M215" s="32" t="n"/>
       <c r="N215" s="32" t="n"/>
       <c r="O215" s="20" t="inlineStr"/>
@@ -11142,11 +12790,23 @@
       <c r="E216" s="20" t="inlineStr"/>
       <c r="F216" s="20" t="inlineStr"/>
       <c r="G216" s="20" t="inlineStr"/>
-      <c r="H216" s="20" t="inlineStr"/>
+      <c r="H216" s="20" t="inlineStr">
+        <is>
+          <t>13,280</t>
+        </is>
+      </c>
       <c r="I216" s="20" t="inlineStr"/>
       <c r="J216" s="20" t="inlineStr"/>
-      <c r="K216" s="32" t="n"/>
-      <c r="L216" s="32" t="inlineStr"/>
+      <c r="K216" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L216" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M216" s="32" t="n"/>
       <c r="N216" s="32" t="n"/>
       <c r="O216" s="20" t="inlineStr"/>
@@ -11228,11 +12888,23 @@
       <c r="E218" s="20" t="inlineStr"/>
       <c r="F218" s="20" t="inlineStr"/>
       <c r="G218" s="20" t="inlineStr"/>
-      <c r="H218" s="20" t="inlineStr"/>
+      <c r="H218" s="20" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
       <c r="I218" s="20" t="inlineStr"/>
       <c r="J218" s="20" t="inlineStr"/>
-      <c r="K218" s="32" t="n"/>
-      <c r="L218" s="32" t="inlineStr"/>
+      <c r="K218" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L218" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M218" s="32" t="n"/>
       <c r="N218" s="32" t="n"/>
       <c r="O218" s="20" t="inlineStr"/>
@@ -11271,11 +12943,23 @@
       <c r="E219" s="20" t="inlineStr"/>
       <c r="F219" s="20" t="inlineStr"/>
       <c r="G219" s="20" t="inlineStr"/>
-      <c r="H219" s="20" t="inlineStr"/>
+      <c r="H219" s="20" t="inlineStr">
+        <is>
+          <t>20,441</t>
+        </is>
+      </c>
       <c r="I219" s="20" t="inlineStr"/>
       <c r="J219" s="20" t="inlineStr"/>
-      <c r="K219" s="32" t="n"/>
-      <c r="L219" s="32" t="inlineStr"/>
+      <c r="K219" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L219" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M219" s="32" t="n"/>
       <c r="N219" s="32" t="n"/>
       <c r="O219" s="20" t="inlineStr"/>
@@ -11357,11 +13041,23 @@
       <c r="E221" s="20" t="inlineStr"/>
       <c r="F221" s="20" t="inlineStr"/>
       <c r="G221" s="20" t="inlineStr"/>
-      <c r="H221" s="20" t="inlineStr"/>
+      <c r="H221" s="20" t="inlineStr">
+        <is>
+          <t>7,607</t>
+        </is>
+      </c>
       <c r="I221" s="20" t="inlineStr"/>
       <c r="J221" s="20" t="inlineStr"/>
-      <c r="K221" s="32" t="n"/>
-      <c r="L221" s="32" t="inlineStr"/>
+      <c r="K221" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L221" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M221" s="32" t="n"/>
       <c r="N221" s="32" t="n"/>
       <c r="O221" s="20" t="inlineStr"/>
@@ -11529,11 +13225,23 @@
       <c r="E225" s="20" t="inlineStr"/>
       <c r="F225" s="20" t="inlineStr"/>
       <c r="G225" s="20" t="inlineStr"/>
-      <c r="H225" s="20" t="inlineStr"/>
+      <c r="H225" s="20" t="inlineStr">
+        <is>
+          <t>16,571</t>
+        </is>
+      </c>
       <c r="I225" s="20" t="inlineStr"/>
       <c r="J225" s="20" t="inlineStr"/>
-      <c r="K225" s="32" t="n"/>
-      <c r="L225" s="32" t="inlineStr"/>
+      <c r="K225" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L225" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M225" s="32" t="n"/>
       <c r="N225" s="32" t="n"/>
       <c r="O225" s="20" t="inlineStr"/>
@@ -11572,11 +13280,23 @@
       <c r="E226" s="20" t="inlineStr"/>
       <c r="F226" s="20" t="inlineStr"/>
       <c r="G226" s="20" t="inlineStr"/>
-      <c r="H226" s="20" t="inlineStr"/>
+      <c r="H226" s="20" t="inlineStr">
+        <is>
+          <t>6,025</t>
+        </is>
+      </c>
       <c r="I226" s="20" t="inlineStr"/>
       <c r="J226" s="20" t="inlineStr"/>
-      <c r="K226" s="32" t="n"/>
-      <c r="L226" s="32" t="inlineStr"/>
+      <c r="K226" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L226" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M226" s="32" t="n"/>
       <c r="N226" s="32" t="n"/>
       <c r="O226" s="20" t="inlineStr"/>
@@ -11615,11 +13335,23 @@
       <c r="E227" s="20" t="inlineStr"/>
       <c r="F227" s="20" t="inlineStr"/>
       <c r="G227" s="20" t="inlineStr"/>
-      <c r="H227" s="20" t="inlineStr"/>
+      <c r="H227" s="20" t="inlineStr">
+        <is>
+          <t>6,528</t>
+        </is>
+      </c>
       <c r="I227" s="20" t="inlineStr"/>
       <c r="J227" s="20" t="inlineStr"/>
-      <c r="K227" s="32" t="n"/>
-      <c r="L227" s="32" t="inlineStr"/>
+      <c r="K227" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L227" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M227" s="32" t="n"/>
       <c r="N227" s="32" t="n"/>
       <c r="O227" s="20" t="inlineStr"/>
@@ -11658,11 +13390,23 @@
       <c r="E228" s="20" t="inlineStr"/>
       <c r="F228" s="20" t="inlineStr"/>
       <c r="G228" s="20" t="inlineStr"/>
-      <c r="H228" s="20" t="inlineStr"/>
+      <c r="H228" s="20" t="inlineStr">
+        <is>
+          <t>1,879</t>
+        </is>
+      </c>
       <c r="I228" s="20" t="inlineStr"/>
       <c r="J228" s="20" t="inlineStr"/>
-      <c r="K228" s="32" t="n"/>
-      <c r="L228" s="32" t="inlineStr"/>
+      <c r="K228" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L228" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M228" s="32" t="n"/>
       <c r="N228" s="32" t="n"/>
       <c r="O228" s="20" t="inlineStr"/>
@@ -11744,11 +13488,23 @@
       <c r="E230" s="20" t="inlineStr"/>
       <c r="F230" s="20" t="inlineStr"/>
       <c r="G230" s="20" t="inlineStr"/>
-      <c r="H230" s="20" t="inlineStr"/>
+      <c r="H230" s="20" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
       <c r="I230" s="20" t="inlineStr"/>
       <c r="J230" s="20" t="inlineStr"/>
-      <c r="K230" s="32" t="n"/>
-      <c r="L230" s="32" t="inlineStr"/>
+      <c r="K230" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L230" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M230" s="32" t="n"/>
       <c r="N230" s="32" t="n"/>
       <c r="O230" s="20" t="inlineStr"/>
@@ -11787,11 +13543,23 @@
       <c r="E231" s="20" t="inlineStr"/>
       <c r="F231" s="20" t="inlineStr"/>
       <c r="G231" s="20" t="inlineStr"/>
-      <c r="H231" s="20" t="inlineStr"/>
+      <c r="H231" s="20" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
       <c r="I231" s="20" t="inlineStr"/>
       <c r="J231" s="20" t="inlineStr"/>
-      <c r="K231" s="32" t="n"/>
-      <c r="L231" s="32" t="inlineStr"/>
+      <c r="K231" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L231" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M231" s="32" t="n"/>
       <c r="N231" s="32" t="n"/>
       <c r="O231" s="20" t="inlineStr"/>
@@ -11830,11 +13598,23 @@
       <c r="E232" s="20" t="inlineStr"/>
       <c r="F232" s="20" t="inlineStr"/>
       <c r="G232" s="20" t="inlineStr"/>
-      <c r="H232" s="20" t="inlineStr"/>
+      <c r="H232" s="20" t="inlineStr">
+        <is>
+          <t>3,246</t>
+        </is>
+      </c>
       <c r="I232" s="20" t="inlineStr"/>
       <c r="J232" s="20" t="inlineStr"/>
-      <c r="K232" s="32" t="n"/>
-      <c r="L232" s="32" t="inlineStr"/>
+      <c r="K232" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L232" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M232" s="32" t="n"/>
       <c r="N232" s="32" t="n"/>
       <c r="O232" s="20" t="inlineStr"/>
@@ -11873,11 +13653,23 @@
       <c r="E233" s="20" t="inlineStr"/>
       <c r="F233" s="20" t="inlineStr"/>
       <c r="G233" s="20" t="inlineStr"/>
-      <c r="H233" s="20" t="inlineStr"/>
+      <c r="H233" s="20" t="inlineStr">
+        <is>
+          <t>3,801</t>
+        </is>
+      </c>
       <c r="I233" s="20" t="inlineStr"/>
       <c r="J233" s="20" t="inlineStr"/>
-      <c r="K233" s="32" t="n"/>
-      <c r="L233" s="32" t="inlineStr"/>
+      <c r="K233" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L233" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M233" s="32" t="n"/>
       <c r="N233" s="32" t="n"/>
       <c r="O233" s="20" t="inlineStr"/>
@@ -12002,11 +13794,23 @@
       <c r="E236" s="20" t="inlineStr"/>
       <c r="F236" s="20" t="inlineStr"/>
       <c r="G236" s="20" t="inlineStr"/>
-      <c r="H236" s="20" t="inlineStr"/>
+      <c r="H236" s="20" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
       <c r="I236" s="20" t="inlineStr"/>
       <c r="J236" s="20" t="inlineStr"/>
-      <c r="K236" s="32" t="n"/>
-      <c r="L236" s="32" t="inlineStr"/>
+      <c r="K236" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L236" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M236" s="32" t="n"/>
       <c r="N236" s="32" t="n"/>
       <c r="O236" s="20" t="inlineStr"/>
@@ -12045,11 +13849,23 @@
       <c r="E237" s="20" t="inlineStr"/>
       <c r="F237" s="20" t="inlineStr"/>
       <c r="G237" s="20" t="inlineStr"/>
-      <c r="H237" s="20" t="inlineStr"/>
+      <c r="H237" s="20" t="inlineStr">
+        <is>
+          <t>16,167</t>
+        </is>
+      </c>
       <c r="I237" s="20" t="inlineStr"/>
       <c r="J237" s="20" t="inlineStr"/>
-      <c r="K237" s="32" t="n"/>
-      <c r="L237" s="32" t="inlineStr"/>
+      <c r="K237" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L237" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M237" s="32" t="n"/>
       <c r="N237" s="32" t="n"/>
       <c r="O237" s="20" t="inlineStr"/>
@@ -12131,11 +13947,23 @@
       <c r="E239" s="20" t="inlineStr"/>
       <c r="F239" s="20" t="inlineStr"/>
       <c r="G239" s="20" t="inlineStr"/>
-      <c r="H239" s="20" t="inlineStr"/>
+      <c r="H239" s="20" t="inlineStr">
+        <is>
+          <t>33,492</t>
+        </is>
+      </c>
       <c r="I239" s="20" t="inlineStr"/>
       <c r="J239" s="20" t="inlineStr"/>
-      <c r="K239" s="32" t="n"/>
-      <c r="L239" s="32" t="inlineStr"/>
+      <c r="K239" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L239" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M239" s="32" t="n"/>
       <c r="N239" s="32" t="n"/>
       <c r="O239" s="20" t="inlineStr"/>
@@ -12174,11 +14002,23 @@
       <c r="E240" s="20" t="inlineStr"/>
       <c r="F240" s="20" t="inlineStr"/>
       <c r="G240" s="20" t="inlineStr"/>
-      <c r="H240" s="20" t="inlineStr"/>
+      <c r="H240" s="20" t="inlineStr">
+        <is>
+          <t>409,360</t>
+        </is>
+      </c>
       <c r="I240" s="20" t="inlineStr"/>
       <c r="J240" s="20" t="inlineStr"/>
-      <c r="K240" s="32" t="n"/>
-      <c r="L240" s="32" t="inlineStr"/>
+      <c r="K240" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L240" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M240" s="32" t="n"/>
       <c r="N240" s="32" t="n"/>
       <c r="O240" s="20" t="inlineStr"/>
@@ -12217,11 +14057,23 @@
       <c r="E241" s="20" t="inlineStr"/>
       <c r="F241" s="20" t="inlineStr"/>
       <c r="G241" s="20" t="inlineStr"/>
-      <c r="H241" s="20" t="inlineStr"/>
+      <c r="H241" s="20" t="inlineStr">
+        <is>
+          <t>85,082</t>
+        </is>
+      </c>
       <c r="I241" s="20" t="inlineStr"/>
       <c r="J241" s="20" t="inlineStr"/>
-      <c r="K241" s="32" t="n"/>
-      <c r="L241" s="32" t="inlineStr"/>
+      <c r="K241" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L241" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M241" s="32" t="n"/>
       <c r="N241" s="32" t="n"/>
       <c r="O241" s="20" t="inlineStr"/>
@@ -12260,11 +14112,23 @@
       <c r="E242" s="20" t="inlineStr"/>
       <c r="F242" s="20" t="inlineStr"/>
       <c r="G242" s="20" t="inlineStr"/>
-      <c r="H242" s="20" t="inlineStr"/>
+      <c r="H242" s="20" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
       <c r="I242" s="20" t="inlineStr"/>
       <c r="J242" s="20" t="inlineStr"/>
-      <c r="K242" s="32" t="n"/>
-      <c r="L242" s="32" t="inlineStr"/>
+      <c r="K242" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L242" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M242" s="32" t="n"/>
       <c r="N242" s="32" t="n"/>
       <c r="O242" s="20" t="inlineStr"/>
@@ -12303,11 +14167,23 @@
       <c r="E243" s="20" t="inlineStr"/>
       <c r="F243" s="20" t="inlineStr"/>
       <c r="G243" s="20" t="inlineStr"/>
-      <c r="H243" s="20" t="inlineStr"/>
+      <c r="H243" s="20" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
       <c r="I243" s="20" t="inlineStr"/>
       <c r="J243" s="20" t="inlineStr"/>
-      <c r="K243" s="32" t="n"/>
-      <c r="L243" s="32" t="inlineStr"/>
+      <c r="K243" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L243" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M243" s="32" t="n"/>
       <c r="N243" s="32" t="n"/>
       <c r="O243" s="20" t="inlineStr"/>
@@ -12389,11 +14265,23 @@
       <c r="E245" s="20" t="inlineStr"/>
       <c r="F245" s="20" t="inlineStr"/>
       <c r="G245" s="20" t="inlineStr"/>
-      <c r="H245" s="20" t="inlineStr"/>
+      <c r="H245" s="20" t="inlineStr">
+        <is>
+          <t>2,319</t>
+        </is>
+      </c>
       <c r="I245" s="20" t="inlineStr"/>
       <c r="J245" s="20" t="inlineStr"/>
-      <c r="K245" s="32" t="n"/>
-      <c r="L245" s="32" t="inlineStr"/>
+      <c r="K245" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L245" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M245" s="32" t="n"/>
       <c r="N245" s="32" t="n"/>
       <c r="O245" s="20" t="inlineStr"/>
@@ -12432,11 +14320,23 @@
       <c r="E246" s="20" t="inlineStr"/>
       <c r="F246" s="20" t="inlineStr"/>
       <c r="G246" s="20" t="inlineStr"/>
-      <c r="H246" s="20" t="inlineStr"/>
+      <c r="H246" s="20" t="inlineStr">
+        <is>
+          <t>15,732</t>
+        </is>
+      </c>
       <c r="I246" s="20" t="inlineStr"/>
       <c r="J246" s="20" t="inlineStr"/>
-      <c r="K246" s="32" t="n"/>
-      <c r="L246" s="32" t="inlineStr"/>
+      <c r="K246" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L246" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M246" s="32" t="n"/>
       <c r="N246" s="32" t="n"/>
       <c r="O246" s="20" t="inlineStr"/>
@@ -12518,11 +14418,23 @@
       <c r="E248" s="20" t="inlineStr"/>
       <c r="F248" s="20" t="inlineStr"/>
       <c r="G248" s="20" t="inlineStr"/>
-      <c r="H248" s="20" t="inlineStr"/>
+      <c r="H248" s="20" t="inlineStr">
+        <is>
+          <t>17,883</t>
+        </is>
+      </c>
       <c r="I248" s="20" t="inlineStr"/>
       <c r="J248" s="20" t="inlineStr"/>
-      <c r="K248" s="32" t="n"/>
-      <c r="L248" s="32" t="inlineStr"/>
+      <c r="K248" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L248" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M248" s="32" t="n"/>
       <c r="N248" s="32" t="n"/>
       <c r="O248" s="20" t="inlineStr"/>
@@ -12604,11 +14516,23 @@
       <c r="E250" s="20" t="inlineStr"/>
       <c r="F250" s="20" t="inlineStr"/>
       <c r="G250" s="20" t="inlineStr"/>
-      <c r="H250" s="20" t="inlineStr"/>
+      <c r="H250" s="20" t="inlineStr">
+        <is>
+          <t>1,706</t>
+        </is>
+      </c>
       <c r="I250" s="20" t="inlineStr"/>
       <c r="J250" s="20" t="inlineStr"/>
-      <c r="K250" s="32" t="n"/>
-      <c r="L250" s="32" t="inlineStr"/>
+      <c r="K250" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L250" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M250" s="32" t="n"/>
       <c r="N250" s="32" t="n"/>
       <c r="O250" s="20" t="inlineStr"/>
@@ -12647,11 +14571,23 @@
       <c r="E251" s="20" t="inlineStr"/>
       <c r="F251" s="20" t="inlineStr"/>
       <c r="G251" s="20" t="inlineStr"/>
-      <c r="H251" s="20" t="inlineStr"/>
+      <c r="H251" s="20" t="inlineStr">
+        <is>
+          <t>19,634</t>
+        </is>
+      </c>
       <c r="I251" s="20" t="inlineStr"/>
       <c r="J251" s="20" t="inlineStr"/>
-      <c r="K251" s="32" t="n"/>
-      <c r="L251" s="32" t="inlineStr"/>
+      <c r="K251" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L251" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M251" s="32" t="n"/>
       <c r="N251" s="32" t="n"/>
       <c r="O251" s="20" t="inlineStr"/>
@@ -12991,11 +14927,23 @@
       <c r="E259" s="20" t="inlineStr"/>
       <c r="F259" s="20" t="inlineStr"/>
       <c r="G259" s="20" t="inlineStr"/>
-      <c r="H259" s="20" t="inlineStr"/>
+      <c r="H259" s="20" t="inlineStr">
+        <is>
+          <t>52,232</t>
+        </is>
+      </c>
       <c r="I259" s="20" t="inlineStr"/>
       <c r="J259" s="20" t="inlineStr"/>
-      <c r="K259" s="32" t="n"/>
-      <c r="L259" s="32" t="inlineStr"/>
+      <c r="K259" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L259" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M259" s="32" t="n"/>
       <c r="N259" s="32" t="n"/>
       <c r="O259" s="20" t="inlineStr"/>
@@ -13335,11 +15283,23 @@
       <c r="E267" s="20" t="inlineStr"/>
       <c r="F267" s="20" t="inlineStr"/>
       <c r="G267" s="20" t="inlineStr"/>
-      <c r="H267" s="20" t="inlineStr"/>
+      <c r="H267" s="20" t="inlineStr">
+        <is>
+          <t>2,633</t>
+        </is>
+      </c>
       <c r="I267" s="20" t="inlineStr"/>
       <c r="J267" s="20" t="inlineStr"/>
-      <c r="K267" s="32" t="n"/>
-      <c r="L267" s="32" t="inlineStr"/>
+      <c r="K267" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L267" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M267" s="32" t="n"/>
       <c r="N267" s="32" t="n"/>
       <c r="O267" s="20" t="inlineStr"/>
@@ -13464,11 +15424,23 @@
       <c r="E270" s="20" t="inlineStr"/>
       <c r="F270" s="20" t="inlineStr"/>
       <c r="G270" s="20" t="inlineStr"/>
-      <c r="H270" s="20" t="inlineStr"/>
+      <c r="H270" s="20" t="inlineStr">
+        <is>
+          <t>4,241</t>
+        </is>
+      </c>
       <c r="I270" s="20" t="inlineStr"/>
       <c r="J270" s="20" t="inlineStr"/>
-      <c r="K270" s="32" t="n"/>
-      <c r="L270" s="32" t="inlineStr"/>
+      <c r="K270" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L270" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M270" s="32" t="n"/>
       <c r="N270" s="32" t="n"/>
       <c r="O270" s="20" t="inlineStr"/>
@@ -13550,11 +15522,23 @@
       <c r="E272" s="20" t="inlineStr"/>
       <c r="F272" s="20" t="inlineStr"/>
       <c r="G272" s="20" t="inlineStr"/>
-      <c r="H272" s="20" t="inlineStr"/>
+      <c r="H272" s="20" t="inlineStr">
+        <is>
+          <t>10,913</t>
+        </is>
+      </c>
       <c r="I272" s="20" t="inlineStr"/>
       <c r="J272" s="20" t="inlineStr"/>
-      <c r="K272" s="32" t="n"/>
-      <c r="L272" s="32" t="inlineStr"/>
+      <c r="K272" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L272" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M272" s="32" t="n"/>
       <c r="N272" s="32" t="n"/>
       <c r="O272" s="20" t="inlineStr"/>
@@ -13593,11 +15577,23 @@
       <c r="E273" s="20" t="inlineStr"/>
       <c r="F273" s="20" t="inlineStr"/>
       <c r="G273" s="20" t="inlineStr"/>
-      <c r="H273" s="20" t="inlineStr"/>
+      <c r="H273" s="20" t="inlineStr">
+        <is>
+          <t>3,099</t>
+        </is>
+      </c>
       <c r="I273" s="20" t="inlineStr"/>
       <c r="J273" s="20" t="inlineStr"/>
-      <c r="K273" s="32" t="n"/>
-      <c r="L273" s="32" t="inlineStr"/>
+      <c r="K273" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L273" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M273" s="32" t="n"/>
       <c r="N273" s="32" t="n"/>
       <c r="O273" s="20" t="inlineStr"/>
@@ -13808,11 +15804,23 @@
       <c r="E278" s="20" t="inlineStr"/>
       <c r="F278" s="20" t="inlineStr"/>
       <c r="G278" s="20" t="inlineStr"/>
-      <c r="H278" s="20" t="inlineStr"/>
+      <c r="H278" s="20" t="inlineStr">
+        <is>
+          <t>78,800</t>
+        </is>
+      </c>
       <c r="I278" s="20" t="inlineStr"/>
       <c r="J278" s="20" t="inlineStr"/>
-      <c r="K278" s="32" t="n"/>
-      <c r="L278" s="32" t="inlineStr"/>
+      <c r="K278" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L278" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M278" s="32" t="n"/>
       <c r="N278" s="32" t="n"/>
       <c r="O278" s="20" t="inlineStr"/>
@@ -13851,11 +15859,23 @@
       <c r="E279" s="20" t="inlineStr"/>
       <c r="F279" s="20" t="inlineStr"/>
       <c r="G279" s="20" t="inlineStr"/>
-      <c r="H279" s="20" t="inlineStr"/>
+      <c r="H279" s="20" t="inlineStr">
+        <is>
+          <t>6,623</t>
+        </is>
+      </c>
       <c r="I279" s="20" t="inlineStr"/>
       <c r="J279" s="20" t="inlineStr"/>
-      <c r="K279" s="32" t="n"/>
-      <c r="L279" s="32" t="inlineStr"/>
+      <c r="K279" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L279" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M279" s="32" t="n"/>
       <c r="N279" s="32" t="n"/>
       <c r="O279" s="20" t="inlineStr"/>
@@ -14023,11 +16043,23 @@
       <c r="E283" s="20" t="inlineStr"/>
       <c r="F283" s="20" t="inlineStr"/>
       <c r="G283" s="20" t="inlineStr"/>
-      <c r="H283" s="20" t="inlineStr"/>
+      <c r="H283" s="20" t="inlineStr">
+        <is>
+          <t>9,920</t>
+        </is>
+      </c>
       <c r="I283" s="20" t="inlineStr"/>
       <c r="J283" s="20" t="inlineStr"/>
-      <c r="K283" s="32" t="n"/>
-      <c r="L283" s="32" t="inlineStr"/>
+      <c r="K283" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L283" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M283" s="32" t="n"/>
       <c r="N283" s="32" t="n"/>
       <c r="O283" s="20" t="inlineStr"/>
@@ -14066,11 +16098,23 @@
       <c r="E284" s="20" t="inlineStr"/>
       <c r="F284" s="20" t="inlineStr"/>
       <c r="G284" s="20" t="inlineStr"/>
-      <c r="H284" s="20" t="inlineStr"/>
+      <c r="H284" s="20" t="inlineStr">
+        <is>
+          <t>17,738</t>
+        </is>
+      </c>
       <c r="I284" s="20" t="inlineStr"/>
       <c r="J284" s="20" t="inlineStr"/>
-      <c r="K284" s="32" t="n"/>
-      <c r="L284" s="32" t="inlineStr"/>
+      <c r="K284" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L284" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M284" s="32" t="n"/>
       <c r="N284" s="32" t="n"/>
       <c r="O284" s="20" t="inlineStr"/>
@@ -14109,11 +16153,23 @@
       <c r="E285" s="20" t="inlineStr"/>
       <c r="F285" s="20" t="inlineStr"/>
       <c r="G285" s="20" t="inlineStr"/>
-      <c r="H285" s="20" t="inlineStr"/>
+      <c r="H285" s="20" t="inlineStr">
+        <is>
+          <t>44,390</t>
+        </is>
+      </c>
       <c r="I285" s="20" t="inlineStr"/>
       <c r="J285" s="20" t="inlineStr"/>
-      <c r="K285" s="32" t="n"/>
-      <c r="L285" s="32" t="inlineStr"/>
+      <c r="K285" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L285" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M285" s="32" t="n"/>
       <c r="N285" s="32" t="n"/>
       <c r="O285" s="20" t="inlineStr"/>
@@ -14195,11 +16251,23 @@
       <c r="E287" s="20" t="inlineStr"/>
       <c r="F287" s="20" t="inlineStr"/>
       <c r="G287" s="20" t="inlineStr"/>
-      <c r="H287" s="20" t="inlineStr"/>
+      <c r="H287" s="20" t="inlineStr">
+        <is>
+          <t>11,911</t>
+        </is>
+      </c>
       <c r="I287" s="20" t="inlineStr"/>
       <c r="J287" s="20" t="inlineStr"/>
-      <c r="K287" s="32" t="n"/>
-      <c r="L287" s="32" t="inlineStr"/>
+      <c r="K287" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L287" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M287" s="32" t="n"/>
       <c r="N287" s="32" t="n"/>
       <c r="O287" s="20" t="inlineStr"/>
@@ -14281,11 +16349,23 @@
       <c r="E289" s="20" t="inlineStr"/>
       <c r="F289" s="20" t="inlineStr"/>
       <c r="G289" s="20" t="inlineStr"/>
-      <c r="H289" s="20" t="inlineStr"/>
+      <c r="H289" s="20" t="inlineStr">
+        <is>
+          <t>23,805</t>
+        </is>
+      </c>
       <c r="I289" s="20" t="inlineStr"/>
       <c r="J289" s="20" t="inlineStr"/>
-      <c r="K289" s="32" t="n"/>
-      <c r="L289" s="32" t="inlineStr"/>
+      <c r="K289" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L289" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M289" s="32" t="n"/>
       <c r="N289" s="32" t="n"/>
       <c r="O289" s="20" t="inlineStr"/>
@@ -14324,11 +16404,23 @@
       <c r="E290" s="20" t="inlineStr"/>
       <c r="F290" s="20" t="inlineStr"/>
       <c r="G290" s="20" t="inlineStr"/>
-      <c r="H290" s="20" t="inlineStr"/>
+      <c r="H290" s="20" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
       <c r="I290" s="20" t="inlineStr"/>
       <c r="J290" s="20" t="inlineStr"/>
-      <c r="K290" s="32" t="n"/>
-      <c r="L290" s="32" t="inlineStr"/>
+      <c r="K290" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L290" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M290" s="32" t="n"/>
       <c r="N290" s="32" t="n"/>
       <c r="O290" s="20" t="inlineStr"/>
@@ -14410,11 +16502,23 @@
       <c r="E292" s="20" t="inlineStr"/>
       <c r="F292" s="20" t="inlineStr"/>
       <c r="G292" s="20" t="inlineStr"/>
-      <c r="H292" s="20" t="inlineStr"/>
+      <c r="H292" s="20" t="inlineStr">
+        <is>
+          <t>2,737</t>
+        </is>
+      </c>
       <c r="I292" s="20" t="inlineStr"/>
       <c r="J292" s="20" t="inlineStr"/>
-      <c r="K292" s="32" t="n"/>
-      <c r="L292" s="32" t="inlineStr"/>
+      <c r="K292" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L292" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M292" s="32" t="n"/>
       <c r="N292" s="32" t="n"/>
       <c r="O292" s="20" t="inlineStr"/>
@@ -14625,11 +16729,23 @@
       <c r="E297" s="20" t="inlineStr"/>
       <c r="F297" s="20" t="inlineStr"/>
       <c r="G297" s="20" t="inlineStr"/>
-      <c r="H297" s="20" t="inlineStr"/>
+      <c r="H297" s="20" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
       <c r="I297" s="20" t="inlineStr"/>
       <c r="J297" s="20" t="inlineStr"/>
-      <c r="K297" s="32" t="n"/>
-      <c r="L297" s="32" t="inlineStr"/>
+      <c r="K297" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L297" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M297" s="32" t="n"/>
       <c r="N297" s="32" t="n"/>
       <c r="O297" s="20" t="inlineStr"/>
@@ -14711,11 +16827,23 @@
       <c r="E299" s="20" t="inlineStr"/>
       <c r="F299" s="20" t="inlineStr"/>
       <c r="G299" s="20" t="inlineStr"/>
-      <c r="H299" s="20" t="inlineStr"/>
+      <c r="H299" s="20" t="inlineStr">
+        <is>
+          <t>9,568</t>
+        </is>
+      </c>
       <c r="I299" s="20" t="inlineStr"/>
       <c r="J299" s="20" t="inlineStr"/>
-      <c r="K299" s="32" t="n"/>
-      <c r="L299" s="32" t="inlineStr"/>
+      <c r="K299" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L299" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M299" s="32" t="n"/>
       <c r="N299" s="32" t="n"/>
       <c r="O299" s="20" t="inlineStr"/>
@@ -14840,11 +16968,23 @@
       <c r="E302" s="20" t="inlineStr"/>
       <c r="F302" s="20" t="inlineStr"/>
       <c r="G302" s="20" t="inlineStr"/>
-      <c r="H302" s="20" t="inlineStr"/>
+      <c r="H302" s="20" t="inlineStr">
+        <is>
+          <t>8,391</t>
+        </is>
+      </c>
       <c r="I302" s="20" t="inlineStr"/>
       <c r="J302" s="20" t="inlineStr"/>
-      <c r="K302" s="32" t="n"/>
-      <c r="L302" s="32" t="inlineStr"/>
+      <c r="K302" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L302" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M302" s="32" t="n"/>
       <c r="N302" s="32" t="n"/>
       <c r="O302" s="20" t="inlineStr"/>
@@ -14926,11 +17066,23 @@
       <c r="E304" s="20" t="inlineStr"/>
       <c r="F304" s="20" t="inlineStr"/>
       <c r="G304" s="20" t="inlineStr"/>
-      <c r="H304" s="20" t="inlineStr"/>
+      <c r="H304" s="20" t="inlineStr">
+        <is>
+          <t>3,370</t>
+        </is>
+      </c>
       <c r="I304" s="20" t="inlineStr"/>
       <c r="J304" s="20" t="inlineStr"/>
-      <c r="K304" s="32" t="n"/>
-      <c r="L304" s="32" t="inlineStr"/>
+      <c r="K304" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L304" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M304" s="32" t="n"/>
       <c r="N304" s="32" t="n"/>
       <c r="O304" s="20" t="inlineStr"/>
@@ -14969,11 +17121,23 @@
       <c r="E305" s="20" t="inlineStr"/>
       <c r="F305" s="20" t="inlineStr"/>
       <c r="G305" s="20" t="inlineStr"/>
-      <c r="H305" s="20" t="inlineStr"/>
+      <c r="H305" s="20" t="inlineStr">
+        <is>
+          <t>1,466</t>
+        </is>
+      </c>
       <c r="I305" s="20" t="inlineStr"/>
       <c r="J305" s="20" t="inlineStr"/>
-      <c r="K305" s="32" t="n"/>
-      <c r="L305" s="32" t="inlineStr"/>
+      <c r="K305" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L305" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M305" s="32" t="n"/>
       <c r="N305" s="32" t="n"/>
       <c r="O305" s="20" t="inlineStr"/>
@@ -15098,11 +17262,23 @@
       <c r="E308" s="20" t="inlineStr"/>
       <c r="F308" s="20" t="inlineStr"/>
       <c r="G308" s="20" t="inlineStr"/>
-      <c r="H308" s="20" t="inlineStr"/>
+      <c r="H308" s="20" t="inlineStr">
+        <is>
+          <t>2,126</t>
+        </is>
+      </c>
       <c r="I308" s="20" t="inlineStr"/>
       <c r="J308" s="20" t="inlineStr"/>
-      <c r="K308" s="32" t="n"/>
-      <c r="L308" s="32" t="inlineStr"/>
+      <c r="K308" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L308" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M308" s="32" t="n"/>
       <c r="N308" s="32" t="n"/>
       <c r="O308" s="20" t="inlineStr"/>
@@ -15141,11 +17317,23 @@
       <c r="E309" s="20" t="inlineStr"/>
       <c r="F309" s="20" t="inlineStr"/>
       <c r="G309" s="20" t="inlineStr"/>
-      <c r="H309" s="20" t="inlineStr"/>
+      <c r="H309" s="20" t="inlineStr">
+        <is>
+          <t>24,646</t>
+        </is>
+      </c>
       <c r="I309" s="20" t="inlineStr"/>
       <c r="J309" s="20" t="inlineStr"/>
-      <c r="K309" s="32" t="n"/>
-      <c r="L309" s="32" t="inlineStr"/>
+      <c r="K309" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L309" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M309" s="32" t="n"/>
       <c r="N309" s="32" t="n"/>
       <c r="O309" s="20" t="inlineStr"/>
@@ -15184,11 +17372,23 @@
       <c r="E310" s="20" t="inlineStr"/>
       <c r="F310" s="20" t="inlineStr"/>
       <c r="G310" s="20" t="inlineStr"/>
-      <c r="H310" s="20" t="inlineStr"/>
+      <c r="H310" s="20" t="inlineStr">
+        <is>
+          <t>9,741</t>
+        </is>
+      </c>
       <c r="I310" s="20" t="inlineStr"/>
       <c r="J310" s="20" t="inlineStr"/>
-      <c r="K310" s="32" t="n"/>
-      <c r="L310" s="32" t="inlineStr"/>
+      <c r="K310" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L310" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M310" s="32" t="n"/>
       <c r="N310" s="32" t="n"/>
       <c r="O310" s="20" t="inlineStr"/>
@@ -15227,11 +17427,23 @@
       <c r="E311" s="20" t="inlineStr"/>
       <c r="F311" s="20" t="inlineStr"/>
       <c r="G311" s="20" t="inlineStr"/>
-      <c r="H311" s="20" t="inlineStr"/>
+      <c r="H311" s="20" t="inlineStr">
+        <is>
+          <t>9,728</t>
+        </is>
+      </c>
       <c r="I311" s="20" t="inlineStr"/>
       <c r="J311" s="20" t="inlineStr"/>
-      <c r="K311" s="32" t="n"/>
-      <c r="L311" s="32" t="inlineStr"/>
+      <c r="K311" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L311" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M311" s="32" t="n"/>
       <c r="N311" s="32" t="n"/>
       <c r="O311" s="20" t="inlineStr"/>
@@ -15270,11 +17482,23 @@
       <c r="E312" s="20" t="inlineStr"/>
       <c r="F312" s="20" t="inlineStr"/>
       <c r="G312" s="20" t="inlineStr"/>
-      <c r="H312" s="20" t="inlineStr"/>
+      <c r="H312" s="20" t="inlineStr">
+        <is>
+          <t>20,865</t>
+        </is>
+      </c>
       <c r="I312" s="20" t="inlineStr"/>
       <c r="J312" s="20" t="inlineStr"/>
-      <c r="K312" s="32" t="n"/>
-      <c r="L312" s="32" t="inlineStr"/>
+      <c r="K312" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L312" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M312" s="32" t="n"/>
       <c r="N312" s="32" t="n"/>
       <c r="O312" s="20" t="inlineStr"/>
@@ -15313,11 +17537,23 @@
       <c r="E313" s="20" t="inlineStr"/>
       <c r="F313" s="20" t="inlineStr"/>
       <c r="G313" s="20" t="inlineStr"/>
-      <c r="H313" s="20" t="inlineStr"/>
+      <c r="H313" s="20" t="inlineStr">
+        <is>
+          <t>45,801</t>
+        </is>
+      </c>
       <c r="I313" s="20" t="inlineStr"/>
       <c r="J313" s="20" t="inlineStr"/>
-      <c r="K313" s="32" t="n"/>
-      <c r="L313" s="32" t="inlineStr"/>
+      <c r="K313" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L313" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M313" s="32" t="n"/>
       <c r="N313" s="32" t="n"/>
       <c r="O313" s="20" t="inlineStr"/>
@@ -15356,11 +17592,23 @@
       <c r="E314" s="20" t="inlineStr"/>
       <c r="F314" s="20" t="inlineStr"/>
       <c r="G314" s="20" t="inlineStr"/>
-      <c r="H314" s="20" t="inlineStr"/>
+      <c r="H314" s="20" t="inlineStr">
+        <is>
+          <t>4,008</t>
+        </is>
+      </c>
       <c r="I314" s="20" t="inlineStr"/>
       <c r="J314" s="20" t="inlineStr"/>
-      <c r="K314" s="32" t="n"/>
-      <c r="L314" s="32" t="inlineStr"/>
+      <c r="K314" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L314" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M314" s="32" t="n"/>
       <c r="N314" s="32" t="n"/>
       <c r="O314" s="20" t="inlineStr"/>
@@ -15399,11 +17647,23 @@
       <c r="E315" s="20" t="inlineStr"/>
       <c r="F315" s="20" t="inlineStr"/>
       <c r="G315" s="20" t="inlineStr"/>
-      <c r="H315" s="20" t="inlineStr"/>
+      <c r="H315" s="20" t="inlineStr">
+        <is>
+          <t>9,017</t>
+        </is>
+      </c>
       <c r="I315" s="20" t="inlineStr"/>
       <c r="J315" s="20" t="inlineStr"/>
-      <c r="K315" s="32" t="n"/>
-      <c r="L315" s="32" t="inlineStr"/>
+      <c r="K315" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L315" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M315" s="32" t="n"/>
       <c r="N315" s="32" t="n"/>
       <c r="O315" s="20" t="inlineStr"/>
@@ -15442,11 +17702,23 @@
       <c r="E316" s="20" t="inlineStr"/>
       <c r="F316" s="20" t="inlineStr"/>
       <c r="G316" s="20" t="inlineStr"/>
-      <c r="H316" s="20" t="inlineStr"/>
+      <c r="H316" s="20" t="inlineStr">
+        <is>
+          <t>4,678</t>
+        </is>
+      </c>
       <c r="I316" s="20" t="inlineStr"/>
       <c r="J316" s="20" t="inlineStr"/>
-      <c r="K316" s="32" t="n"/>
-      <c r="L316" s="32" t="inlineStr"/>
+      <c r="K316" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L316" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M316" s="32" t="n"/>
       <c r="N316" s="32" t="n"/>
       <c r="O316" s="20" t="inlineStr"/>
@@ -15528,11 +17800,23 @@
       <c r="E318" s="20" t="inlineStr"/>
       <c r="F318" s="20" t="inlineStr"/>
       <c r="G318" s="20" t="inlineStr"/>
-      <c r="H318" s="20" t="inlineStr"/>
+      <c r="H318" s="20" t="inlineStr">
+        <is>
+          <t>5,838</t>
+        </is>
+      </c>
       <c r="I318" s="20" t="inlineStr"/>
       <c r="J318" s="20" t="inlineStr"/>
-      <c r="K318" s="32" t="n"/>
-      <c r="L318" s="32" t="inlineStr"/>
+      <c r="K318" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L318" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M318" s="32" t="n"/>
       <c r="N318" s="32" t="n"/>
       <c r="O318" s="20" t="inlineStr"/>
@@ -15571,11 +17855,23 @@
       <c r="E319" s="20" t="inlineStr"/>
       <c r="F319" s="20" t="inlineStr"/>
       <c r="G319" s="20" t="inlineStr"/>
-      <c r="H319" s="20" t="inlineStr"/>
+      <c r="H319" s="20" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
       <c r="I319" s="20" t="inlineStr"/>
       <c r="J319" s="20" t="inlineStr"/>
-      <c r="K319" s="32" t="n"/>
-      <c r="L319" s="32" t="inlineStr"/>
+      <c r="K319" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L319" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M319" s="32" t="n"/>
       <c r="N319" s="32" t="n"/>
       <c r="O319" s="20" t="inlineStr"/>
@@ -15614,11 +17910,23 @@
       <c r="E320" s="20" t="inlineStr"/>
       <c r="F320" s="20" t="inlineStr"/>
       <c r="G320" s="20" t="inlineStr"/>
-      <c r="H320" s="20" t="inlineStr"/>
+      <c r="H320" s="20" t="inlineStr">
+        <is>
+          <t>26,514</t>
+        </is>
+      </c>
       <c r="I320" s="20" t="inlineStr"/>
       <c r="J320" s="20" t="inlineStr"/>
-      <c r="K320" s="32" t="n"/>
-      <c r="L320" s="32" t="inlineStr"/>
+      <c r="K320" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L320" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M320" s="32" t="n"/>
       <c r="N320" s="32" t="n"/>
       <c r="O320" s="20" t="inlineStr"/>
@@ -15657,11 +17965,23 @@
       <c r="E321" s="20" t="inlineStr"/>
       <c r="F321" s="20" t="inlineStr"/>
       <c r="G321" s="20" t="inlineStr"/>
-      <c r="H321" s="20" t="inlineStr"/>
+      <c r="H321" s="20" t="inlineStr">
+        <is>
+          <t>30,679</t>
+        </is>
+      </c>
       <c r="I321" s="20" t="inlineStr"/>
       <c r="J321" s="20" t="inlineStr"/>
-      <c r="K321" s="32" t="n"/>
-      <c r="L321" s="32" t="inlineStr"/>
+      <c r="K321" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L321" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M321" s="32" t="n"/>
       <c r="N321" s="32" t="n"/>
       <c r="O321" s="20" t="inlineStr"/>
@@ -15700,11 +18020,23 @@
       <c r="E322" s="20" t="inlineStr"/>
       <c r="F322" s="20" t="inlineStr"/>
       <c r="G322" s="20" t="inlineStr"/>
-      <c r="H322" s="20" t="inlineStr"/>
+      <c r="H322" s="20" t="inlineStr">
+        <is>
+          <t>54,740</t>
+        </is>
+      </c>
       <c r="I322" s="20" t="inlineStr"/>
       <c r="J322" s="20" t="inlineStr"/>
-      <c r="K322" s="32" t="n"/>
-      <c r="L322" s="32" t="inlineStr"/>
+      <c r="K322" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L322" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M322" s="7" t="inlineStr">
         <is>
           <t>IN ORBIT: Tape B 20x</t>
@@ -15747,11 +18079,23 @@
       <c r="E323" s="20" t="inlineStr"/>
       <c r="F323" s="20" t="inlineStr"/>
       <c r="G323" s="20" t="inlineStr"/>
-      <c r="H323" s="20" t="inlineStr"/>
+      <c r="H323" s="20" t="inlineStr">
+        <is>
+          <t>19,021</t>
+        </is>
+      </c>
       <c r="I323" s="20" t="inlineStr"/>
       <c r="J323" s="20" t="inlineStr"/>
-      <c r="K323" s="32" t="n"/>
-      <c r="L323" s="32" t="inlineStr"/>
+      <c r="K323" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L323" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M323" s="32" t="n"/>
       <c r="N323" s="32" t="n"/>
       <c r="O323" s="20" t="inlineStr"/>
@@ -15790,11 +18134,23 @@
       <c r="E324" s="20" t="inlineStr"/>
       <c r="F324" s="20" t="inlineStr"/>
       <c r="G324" s="20" t="inlineStr"/>
-      <c r="H324" s="20" t="inlineStr"/>
+      <c r="H324" s="20" t="inlineStr">
+        <is>
+          <t>73,206</t>
+        </is>
+      </c>
       <c r="I324" s="20" t="inlineStr"/>
       <c r="J324" s="20" t="inlineStr"/>
-      <c r="K324" s="32" t="n"/>
-      <c r="L324" s="32" t="inlineStr"/>
+      <c r="K324" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L324" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M324" s="7" t="inlineStr">
         <is>
           <t>IN ORBIT: INZO 12x</t>
@@ -15837,11 +18193,23 @@
       <c r="E325" s="20" t="inlineStr"/>
       <c r="F325" s="20" t="inlineStr"/>
       <c r="G325" s="20" t="inlineStr"/>
-      <c r="H325" s="20" t="inlineStr"/>
+      <c r="H325" s="20" t="inlineStr">
+        <is>
+          <t>42,923</t>
+        </is>
+      </c>
       <c r="I325" s="20" t="inlineStr"/>
       <c r="J325" s="20" t="inlineStr"/>
-      <c r="K325" s="32" t="n"/>
-      <c r="L325" s="32" t="inlineStr"/>
+      <c r="K325" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L325" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M325" s="32" t="n"/>
       <c r="N325" s="32" t="n"/>
       <c r="O325" s="20" t="inlineStr"/>
@@ -15880,11 +18248,23 @@
       <c r="E326" s="20" t="inlineStr"/>
       <c r="F326" s="20" t="inlineStr"/>
       <c r="G326" s="20" t="inlineStr"/>
-      <c r="H326" s="20" t="inlineStr"/>
+      <c r="H326" s="20" t="inlineStr">
+        <is>
+          <t>15,201</t>
+        </is>
+      </c>
       <c r="I326" s="20" t="inlineStr"/>
       <c r="J326" s="20" t="inlineStr"/>
-      <c r="K326" s="32" t="n"/>
-      <c r="L326" s="32" t="inlineStr"/>
+      <c r="K326" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L326" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M326" s="32" t="n"/>
       <c r="N326" s="32" t="n"/>
       <c r="O326" s="20" t="inlineStr"/>
@@ -15923,11 +18303,23 @@
       <c r="E327" s="20" t="inlineStr"/>
       <c r="F327" s="20" t="inlineStr"/>
       <c r="G327" s="20" t="inlineStr"/>
-      <c r="H327" s="20" t="inlineStr"/>
+      <c r="H327" s="20" t="inlineStr">
+        <is>
+          <t>50,833</t>
+        </is>
+      </c>
       <c r="I327" s="20" t="inlineStr"/>
       <c r="J327" s="20" t="inlineStr"/>
-      <c r="K327" s="32" t="n"/>
-      <c r="L327" s="32" t="inlineStr"/>
+      <c r="K327" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L327" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M327" s="32" t="n"/>
       <c r="N327" s="32" t="n"/>
       <c r="O327" s="20" t="inlineStr"/>
@@ -15966,11 +18358,23 @@
       <c r="E328" s="20" t="inlineStr"/>
       <c r="F328" s="20" t="inlineStr"/>
       <c r="G328" s="20" t="inlineStr"/>
-      <c r="H328" s="20" t="inlineStr"/>
+      <c r="H328" s="20" t="inlineStr">
+        <is>
+          <t>8,484</t>
+        </is>
+      </c>
       <c r="I328" s="20" t="inlineStr"/>
       <c r="J328" s="20" t="inlineStr"/>
-      <c r="K328" s="32" t="n"/>
-      <c r="L328" s="32" t="inlineStr"/>
+      <c r="K328" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L328" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M328" s="32" t="n"/>
       <c r="N328" s="32" t="n"/>
       <c r="O328" s="20" t="inlineStr"/>
@@ -16009,11 +18413,23 @@
       <c r="E329" s="20" t="inlineStr"/>
       <c r="F329" s="20" t="inlineStr"/>
       <c r="G329" s="20" t="inlineStr"/>
-      <c r="H329" s="20" t="inlineStr"/>
+      <c r="H329" s="20" t="inlineStr">
+        <is>
+          <t>1,381</t>
+        </is>
+      </c>
       <c r="I329" s="20" t="inlineStr"/>
       <c r="J329" s="20" t="inlineStr"/>
-      <c r="K329" s="32" t="n"/>
-      <c r="L329" s="32" t="inlineStr"/>
+      <c r="K329" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L329" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M329" s="32" t="n"/>
       <c r="N329" s="32" t="n"/>
       <c r="O329" s="20" t="inlineStr"/>
@@ -16052,11 +18468,23 @@
       <c r="E330" s="20" t="inlineStr"/>
       <c r="F330" s="20" t="inlineStr"/>
       <c r="G330" s="20" t="inlineStr"/>
-      <c r="H330" s="20" t="inlineStr"/>
+      <c r="H330" s="20" t="inlineStr">
+        <is>
+          <t>936</t>
+        </is>
+      </c>
       <c r="I330" s="20" t="inlineStr"/>
       <c r="J330" s="20" t="inlineStr"/>
-      <c r="K330" s="32" t="n"/>
-      <c r="L330" s="32" t="inlineStr"/>
+      <c r="K330" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L330" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M330" s="32" t="n"/>
       <c r="N330" s="32" t="n"/>
       <c r="O330" s="20" t="inlineStr"/>
@@ -16095,11 +18523,23 @@
       <c r="E331" s="20" t="inlineStr"/>
       <c r="F331" s="20" t="inlineStr"/>
       <c r="G331" s="20" t="inlineStr"/>
-      <c r="H331" s="20" t="inlineStr"/>
+      <c r="H331" s="20" t="inlineStr">
+        <is>
+          <t>963</t>
+        </is>
+      </c>
       <c r="I331" s="20" t="inlineStr"/>
       <c r="J331" s="20" t="inlineStr"/>
-      <c r="K331" s="32" t="n"/>
-      <c r="L331" s="32" t="inlineStr"/>
+      <c r="K331" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L331" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M331" s="32" t="n"/>
       <c r="N331" s="32" t="n"/>
       <c r="O331" s="20" t="inlineStr"/>
@@ -16138,11 +18578,23 @@
       <c r="E332" s="20" t="inlineStr"/>
       <c r="F332" s="20" t="inlineStr"/>
       <c r="G332" s="20" t="inlineStr"/>
-      <c r="H332" s="20" t="inlineStr"/>
+      <c r="H332" s="20" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
       <c r="I332" s="20" t="inlineStr"/>
       <c r="J332" s="20" t="inlineStr"/>
-      <c r="K332" s="32" t="n"/>
-      <c r="L332" s="32" t="inlineStr"/>
+      <c r="K332" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L332" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M332" s="32" t="n"/>
       <c r="N332" s="32" t="n"/>
       <c r="O332" s="20" t="inlineStr"/>
@@ -16181,11 +18633,23 @@
       <c r="E333" s="20" t="inlineStr"/>
       <c r="F333" s="20" t="inlineStr"/>
       <c r="G333" s="20" t="inlineStr"/>
-      <c r="H333" s="20" t="inlineStr"/>
+      <c r="H333" s="20" t="inlineStr">
+        <is>
+          <t>3,936</t>
+        </is>
+      </c>
       <c r="I333" s="20" t="inlineStr"/>
       <c r="J333" s="20" t="inlineStr"/>
-      <c r="K333" s="32" t="n"/>
-      <c r="L333" s="32" t="inlineStr"/>
+      <c r="K333" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L333" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M333" s="32" t="n"/>
       <c r="N333" s="32" t="n"/>
       <c r="O333" s="20" t="inlineStr"/>
@@ -16224,11 +18688,23 @@
       <c r="E334" s="20" t="inlineStr"/>
       <c r="F334" s="20" t="inlineStr"/>
       <c r="G334" s="20" t="inlineStr"/>
-      <c r="H334" s="20" t="inlineStr"/>
+      <c r="H334" s="20" t="inlineStr">
+        <is>
+          <t>16,500</t>
+        </is>
+      </c>
       <c r="I334" s="20" t="inlineStr"/>
       <c r="J334" s="20" t="inlineStr"/>
-      <c r="K334" s="32" t="n"/>
-      <c r="L334" s="32" t="inlineStr"/>
+      <c r="K334" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L334" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M334" s="32" t="n"/>
       <c r="N334" s="32" t="n"/>
       <c r="O334" s="20" t="inlineStr"/>
@@ -16310,11 +18786,23 @@
       <c r="E336" s="20" t="inlineStr"/>
       <c r="F336" s="20" t="inlineStr"/>
       <c r="G336" s="20" t="inlineStr"/>
-      <c r="H336" s="20" t="inlineStr"/>
+      <c r="H336" s="20" t="inlineStr">
+        <is>
+          <t>23,564</t>
+        </is>
+      </c>
       <c r="I336" s="20" t="inlineStr"/>
       <c r="J336" s="20" t="inlineStr"/>
-      <c r="K336" s="32" t="n"/>
-      <c r="L336" s="32" t="inlineStr"/>
+      <c r="K336" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L336" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M336" s="32" t="n"/>
       <c r="N336" s="32" t="n"/>
       <c r="O336" s="20" t="inlineStr"/>
@@ -16353,11 +18841,23 @@
       <c r="E337" s="20" t="inlineStr"/>
       <c r="F337" s="20" t="inlineStr"/>
       <c r="G337" s="20" t="inlineStr"/>
-      <c r="H337" s="20" t="inlineStr"/>
+      <c r="H337" s="20" t="inlineStr">
+        <is>
+          <t>62,369</t>
+        </is>
+      </c>
       <c r="I337" s="20" t="inlineStr"/>
       <c r="J337" s="20" t="inlineStr"/>
-      <c r="K337" s="32" t="n"/>
-      <c r="L337" s="32" t="inlineStr"/>
+      <c r="K337" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L337" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M337" s="32" t="n"/>
       <c r="N337" s="32" t="n"/>
       <c r="O337" s="20" t="inlineStr"/>
@@ -16396,11 +18896,23 @@
       <c r="E338" s="20" t="inlineStr"/>
       <c r="F338" s="20" t="inlineStr"/>
       <c r="G338" s="20" t="inlineStr"/>
-      <c r="H338" s="20" t="inlineStr"/>
+      <c r="H338" s="20" t="inlineStr">
+        <is>
+          <t>5,228</t>
+        </is>
+      </c>
       <c r="I338" s="20" t="inlineStr"/>
       <c r="J338" s="20" t="inlineStr"/>
-      <c r="K338" s="32" t="n"/>
-      <c r="L338" s="32" t="inlineStr"/>
+      <c r="K338" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L338" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M338" s="32" t="n"/>
       <c r="N338" s="32" t="n"/>
       <c r="O338" s="20" t="inlineStr"/>
@@ -16482,11 +18994,23 @@
       <c r="E340" s="20" t="inlineStr"/>
       <c r="F340" s="20" t="inlineStr"/>
       <c r="G340" s="20" t="inlineStr"/>
-      <c r="H340" s="20" t="inlineStr"/>
+      <c r="H340" s="20" t="inlineStr">
+        <is>
+          <t>14,699</t>
+        </is>
+      </c>
       <c r="I340" s="20" t="inlineStr"/>
       <c r="J340" s="20" t="inlineStr"/>
-      <c r="K340" s="32" t="n"/>
-      <c r="L340" s="32" t="inlineStr"/>
+      <c r="K340" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L340" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M340" s="32" t="n"/>
       <c r="N340" s="32" t="n"/>
       <c r="O340" s="20" t="inlineStr"/>
@@ -16525,11 +19049,23 @@
       <c r="E341" s="20" t="inlineStr"/>
       <c r="F341" s="20" t="inlineStr"/>
       <c r="G341" s="20" t="inlineStr"/>
-      <c r="H341" s="20" t="inlineStr"/>
+      <c r="H341" s="20" t="inlineStr">
+        <is>
+          <t>1,885</t>
+        </is>
+      </c>
       <c r="I341" s="20" t="inlineStr"/>
       <c r="J341" s="20" t="inlineStr"/>
-      <c r="K341" s="32" t="n"/>
-      <c r="L341" s="32" t="inlineStr"/>
+      <c r="K341" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L341" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M341" s="32" t="n"/>
       <c r="N341" s="32" t="n"/>
       <c r="O341" s="20" t="inlineStr"/>
@@ -16568,11 +19104,23 @@
       <c r="E342" s="20" t="inlineStr"/>
       <c r="F342" s="20" t="inlineStr"/>
       <c r="G342" s="20" t="inlineStr"/>
-      <c r="H342" s="20" t="inlineStr"/>
+      <c r="H342" s="20" t="inlineStr">
+        <is>
+          <t>843</t>
+        </is>
+      </c>
       <c r="I342" s="20" t="inlineStr"/>
       <c r="J342" s="20" t="inlineStr"/>
-      <c r="K342" s="32" t="n"/>
-      <c r="L342" s="32" t="inlineStr"/>
+      <c r="K342" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L342" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M342" s="32" t="n"/>
       <c r="N342" s="32" t="n"/>
       <c r="O342" s="20" t="inlineStr"/>
@@ -16611,11 +19159,23 @@
       <c r="E343" s="20" t="inlineStr"/>
       <c r="F343" s="20" t="inlineStr"/>
       <c r="G343" s="20" t="inlineStr"/>
-      <c r="H343" s="20" t="inlineStr"/>
+      <c r="H343" s="20" t="inlineStr">
+        <is>
+          <t>5,355</t>
+        </is>
+      </c>
       <c r="I343" s="20" t="inlineStr"/>
       <c r="J343" s="20" t="inlineStr"/>
-      <c r="K343" s="32" t="n"/>
-      <c r="L343" s="32" t="inlineStr"/>
+      <c r="K343" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L343" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M343" s="32" t="n"/>
       <c r="N343" s="32" t="n"/>
       <c r="O343" s="20" t="inlineStr"/>
@@ -16654,11 +19214,23 @@
       <c r="E344" s="20" t="inlineStr"/>
       <c r="F344" s="20" t="inlineStr"/>
       <c r="G344" s="20" t="inlineStr"/>
-      <c r="H344" s="20" t="inlineStr"/>
+      <c r="H344" s="20" t="inlineStr">
+        <is>
+          <t>24,609</t>
+        </is>
+      </c>
       <c r="I344" s="20" t="inlineStr"/>
       <c r="J344" s="20" t="inlineStr"/>
-      <c r="K344" s="32" t="n"/>
-      <c r="L344" s="32" t="inlineStr"/>
+      <c r="K344" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L344" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M344" s="32" t="n"/>
       <c r="N344" s="32" t="n"/>
       <c r="O344" s="20" t="inlineStr"/>
@@ -16697,11 +19269,23 @@
       <c r="E345" s="20" t="inlineStr"/>
       <c r="F345" s="20" t="inlineStr"/>
       <c r="G345" s="20" t="inlineStr"/>
-      <c r="H345" s="20" t="inlineStr"/>
+      <c r="H345" s="20" t="inlineStr">
+        <is>
+          <t>36,628</t>
+        </is>
+      </c>
       <c r="I345" s="20" t="inlineStr"/>
       <c r="J345" s="20" t="inlineStr"/>
-      <c r="K345" s="32" t="n"/>
-      <c r="L345" s="32" t="inlineStr"/>
+      <c r="K345" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L345" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M345" s="32" t="n"/>
       <c r="N345" s="32" t="n"/>
       <c r="O345" s="20" t="inlineStr"/>
@@ -16740,11 +19324,23 @@
       <c r="E346" s="20" t="inlineStr"/>
       <c r="F346" s="20" t="inlineStr"/>
       <c r="G346" s="20" t="inlineStr"/>
-      <c r="H346" s="20" t="inlineStr"/>
+      <c r="H346" s="20" t="inlineStr">
+        <is>
+          <t>38,328</t>
+        </is>
+      </c>
       <c r="I346" s="20" t="inlineStr"/>
       <c r="J346" s="20" t="inlineStr"/>
-      <c r="K346" s="32" t="n"/>
-      <c r="L346" s="32" t="inlineStr"/>
+      <c r="K346" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L346" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M346" s="32" t="n"/>
       <c r="N346" s="32" t="n"/>
       <c r="O346" s="20" t="inlineStr"/>
@@ -16783,11 +19379,23 @@
       <c r="E347" s="20" t="inlineStr"/>
       <c r="F347" s="20" t="inlineStr"/>
       <c r="G347" s="20" t="inlineStr"/>
-      <c r="H347" s="20" t="inlineStr"/>
+      <c r="H347" s="20" t="inlineStr">
+        <is>
+          <t>3,570</t>
+        </is>
+      </c>
       <c r="I347" s="20" t="inlineStr"/>
       <c r="J347" s="20" t="inlineStr"/>
-      <c r="K347" s="32" t="n"/>
-      <c r="L347" s="32" t="inlineStr"/>
+      <c r="K347" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L347" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M347" s="32" t="n"/>
       <c r="N347" s="32" t="n"/>
       <c r="O347" s="20" t="inlineStr"/>
@@ -16826,11 +19434,23 @@
       <c r="E348" s="20" t="inlineStr"/>
       <c r="F348" s="20" t="inlineStr"/>
       <c r="G348" s="20" t="inlineStr"/>
-      <c r="H348" s="20" t="inlineStr"/>
+      <c r="H348" s="20" t="inlineStr">
+        <is>
+          <t>4,892</t>
+        </is>
+      </c>
       <c r="I348" s="20" t="inlineStr"/>
       <c r="J348" s="20" t="inlineStr"/>
-      <c r="K348" s="32" t="n"/>
-      <c r="L348" s="32" t="inlineStr"/>
+      <c r="K348" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L348" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M348" s="32" t="n"/>
       <c r="N348" s="32" t="n"/>
       <c r="O348" s="20" t="inlineStr"/>
@@ -16869,11 +19489,23 @@
       <c r="E349" s="20" t="inlineStr"/>
       <c r="F349" s="20" t="inlineStr"/>
       <c r="G349" s="20" t="inlineStr"/>
-      <c r="H349" s="20" t="inlineStr"/>
+      <c r="H349" s="20" t="inlineStr">
+        <is>
+          <t>19,451</t>
+        </is>
+      </c>
       <c r="I349" s="20" t="inlineStr"/>
       <c r="J349" s="20" t="inlineStr"/>
-      <c r="K349" s="32" t="n"/>
-      <c r="L349" s="32" t="inlineStr"/>
+      <c r="K349" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L349" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M349" s="32" t="n"/>
       <c r="N349" s="32" t="n"/>
       <c r="O349" s="20" t="inlineStr"/>
@@ -16912,11 +19544,23 @@
       <c r="E350" s="20" t="inlineStr"/>
       <c r="F350" s="20" t="inlineStr"/>
       <c r="G350" s="20" t="inlineStr"/>
-      <c r="H350" s="20" t="inlineStr"/>
+      <c r="H350" s="20" t="inlineStr">
+        <is>
+          <t>7,015</t>
+        </is>
+      </c>
       <c r="I350" s="20" t="inlineStr"/>
       <c r="J350" s="20" t="inlineStr"/>
-      <c r="K350" s="32" t="n"/>
-      <c r="L350" s="32" t="inlineStr"/>
+      <c r="K350" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L350" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M350" s="32" t="n"/>
       <c r="N350" s="32" t="n"/>
       <c r="O350" s="20" t="inlineStr"/>
@@ -16955,11 +19599,23 @@
       <c r="E351" s="20" t="inlineStr"/>
       <c r="F351" s="20" t="inlineStr"/>
       <c r="G351" s="20" t="inlineStr"/>
-      <c r="H351" s="20" t="inlineStr"/>
+      <c r="H351" s="20" t="inlineStr">
+        <is>
+          <t>13,547</t>
+        </is>
+      </c>
       <c r="I351" s="20" t="inlineStr"/>
       <c r="J351" s="20" t="inlineStr"/>
-      <c r="K351" s="32" t="n"/>
-      <c r="L351" s="32" t="inlineStr"/>
+      <c r="K351" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L351" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M351" s="32" t="n"/>
       <c r="N351" s="32" t="n"/>
       <c r="O351" s="20" t="inlineStr"/>
@@ -16998,11 +19654,23 @@
       <c r="E352" s="20" t="inlineStr"/>
       <c r="F352" s="20" t="inlineStr"/>
       <c r="G352" s="20" t="inlineStr"/>
-      <c r="H352" s="20" t="inlineStr"/>
+      <c r="H352" s="20" t="inlineStr">
+        <is>
+          <t>10,131</t>
+        </is>
+      </c>
       <c r="I352" s="20" t="inlineStr"/>
       <c r="J352" s="20" t="inlineStr"/>
-      <c r="K352" s="32" t="n"/>
-      <c r="L352" s="32" t="inlineStr"/>
+      <c r="K352" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L352" s="38" t="inlineStr">
+        <is>
+          <t>IN CURRENCY - a booking is worth a lot here</t>
+        </is>
+      </c>
       <c r="M352" s="32" t="n"/>
       <c r="N352" s="32" t="n"/>
       <c r="O352" s="20" t="inlineStr"/>
@@ -17041,11 +19709,23 @@
       <c r="E353" s="20" t="inlineStr"/>
       <c r="F353" s="20" t="inlineStr"/>
       <c r="G353" s="20" t="inlineStr"/>
-      <c r="H353" s="20" t="inlineStr"/>
+      <c r="H353" s="20" t="inlineStr">
+        <is>
+          <t>1,970</t>
+        </is>
+      </c>
       <c r="I353" s="20" t="inlineStr"/>
       <c r="J353" s="20" t="inlineStr"/>
-      <c r="K353" s="32" t="n"/>
-      <c r="L353" s="32" t="inlineStr"/>
+      <c r="K353" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L353" s="28" t="inlineStr">
+        <is>
+          <t>Below - too small to borrow reach</t>
+        </is>
+      </c>
       <c r="M353" s="32" t="n"/>
       <c r="N353" s="32" t="n"/>
       <c r="O353" s="20" t="inlineStr"/>
@@ -17084,11 +19764,23 @@
       <c r="E354" s="23" t="inlineStr"/>
       <c r="F354" s="23" t="inlineStr"/>
       <c r="G354" s="23" t="inlineStr"/>
-      <c r="H354" s="23" t="inlineStr"/>
+      <c r="H354" s="23" t="inlineStr">
+        <is>
+          <t>34,281</t>
+        </is>
+      </c>
       <c r="I354" s="23" t="inlineStr"/>
       <c r="J354" s="23" t="inlineStr"/>
-      <c r="K354" s="32" t="n"/>
-      <c r="L354" s="32" t="inlineStr"/>
+      <c r="K354" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L354" s="39" t="inlineStr">
+        <is>
+          <t>Edge - booking still means something</t>
+        </is>
+      </c>
       <c r="M354" s="32" t="n"/>
       <c r="N354" s="38" t="inlineStr">
         <is>
@@ -17135,11 +19827,23 @@
       <c r="E355" s="23" t="inlineStr"/>
       <c r="F355" s="23" t="inlineStr"/>
       <c r="G355" s="23" t="inlineStr"/>
-      <c r="H355" s="23" t="inlineStr"/>
+      <c r="H355" s="23" t="inlineStr">
+        <is>
+          <t>97,336</t>
+        </is>
+      </c>
       <c r="I355" s="23" t="inlineStr"/>
       <c r="J355" s="23" t="inlineStr"/>
-      <c r="K355" s="32" t="n"/>
-      <c r="L355" s="32" t="inlineStr"/>
+      <c r="K355" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L355" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M355" s="7" t="inlineStr">
         <is>
           <t>HUB. CloZee 37x, CharlesTheFirst 26x, Freddy Todd 25x, Tripp St. 24x, EAZYBAKED 23x</t>
@@ -17190,11 +19894,23 @@
       <c r="E356" s="23" t="inlineStr"/>
       <c r="F356" s="23" t="inlineStr"/>
       <c r="G356" s="23" t="inlineStr"/>
-      <c r="H356" s="23" t="inlineStr"/>
+      <c r="H356" s="23" t="inlineStr">
+        <is>
+          <t>55,185</t>
+        </is>
+      </c>
       <c r="I356" s="23" t="inlineStr"/>
       <c r="J356" s="23" t="inlineStr"/>
-      <c r="K356" s="32" t="n"/>
-      <c r="L356" s="32" t="inlineStr"/>
+      <c r="K356" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L356" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M356" s="7" t="inlineStr">
         <is>
           <t>IN ORBIT: Of The Trees 23x (no block of his own)</t>
@@ -17245,11 +19961,23 @@
       <c r="E357" s="23" t="inlineStr"/>
       <c r="F357" s="23" t="inlineStr"/>
       <c r="G357" s="23" t="inlineStr"/>
-      <c r="H357" s="23" t="inlineStr"/>
+      <c r="H357" s="23" t="inlineStr">
+        <is>
+          <t>163,091</t>
+        </is>
+      </c>
       <c r="I357" s="23" t="inlineStr"/>
       <c r="J357" s="23" t="inlineStr"/>
-      <c r="K357" s="32" t="n"/>
-      <c r="L357" s="32" t="inlineStr"/>
+      <c r="K357" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L357" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M357" s="7" t="inlineStr">
         <is>
           <t>HUB. Subtronics 22x, Liquid Stranger 20x, Effin 20x, Ravenscoon 17x, Wooli 15x</t>
@@ -17300,11 +20028,23 @@
       <c r="E358" s="23" t="inlineStr"/>
       <c r="F358" s="23" t="inlineStr"/>
       <c r="G358" s="23" t="inlineStr"/>
-      <c r="H358" s="23" t="inlineStr"/>
+      <c r="H358" s="23" t="inlineStr">
+        <is>
+          <t>41,766</t>
+        </is>
+      </c>
       <c r="I358" s="23" t="inlineStr"/>
       <c r="J358" s="23" t="inlineStr"/>
-      <c r="K358" s="32" t="n"/>
-      <c r="L358" s="32" t="inlineStr"/>
+      <c r="K358" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L358" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M358" s="32" t="n"/>
       <c r="N358" s="38" t="inlineStr">
         <is>
@@ -17351,11 +20091,23 @@
       <c r="E359" s="23" t="inlineStr"/>
       <c r="F359" s="23" t="inlineStr"/>
       <c r="G359" s="23" t="inlineStr"/>
-      <c r="H359" s="23" t="inlineStr"/>
+      <c r="H359" s="23" t="inlineStr">
+        <is>
+          <t>65,277</t>
+        </is>
+      </c>
       <c r="I359" s="23" t="inlineStr"/>
       <c r="J359" s="23" t="inlineStr"/>
-      <c r="K359" s="32" t="n"/>
-      <c r="L359" s="32" t="inlineStr"/>
+      <c r="K359" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L359" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M359" s="7" t="inlineStr">
         <is>
           <t>HUB. Liquid Stranger 13x, Dirt Monkey 12x, Mersiv 12x, HYDRAULIX 10x, Blookah 9x</t>
@@ -17406,11 +20158,23 @@
       <c r="E360" s="23" t="inlineStr"/>
       <c r="F360" s="23" t="inlineStr"/>
       <c r="G360" s="23" t="inlineStr"/>
-      <c r="H360" s="23" t="inlineStr"/>
+      <c r="H360" s="23" t="inlineStr">
+        <is>
+          <t>87,032</t>
+        </is>
+      </c>
       <c r="I360" s="23" t="inlineStr"/>
       <c r="J360" s="23" t="inlineStr"/>
-      <c r="K360" s="32" t="n"/>
-      <c r="L360" s="32" t="inlineStr"/>
+      <c r="K360" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L360" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M360" s="7" t="inlineStr">
         <is>
           <t>HUB. CloZee 61x, Liquid Stranger 51x, Zingara 50x, G-REX 38x, Champagne Drip 25x</t>
@@ -17457,11 +20221,23 @@
       <c r="E361" s="23" t="inlineStr"/>
       <c r="F361" s="23" t="inlineStr"/>
       <c r="G361" s="23" t="inlineStr"/>
-      <c r="H361" s="23" t="inlineStr"/>
+      <c r="H361" s="23" t="inlineStr">
+        <is>
+          <t>61,811</t>
+        </is>
+      </c>
       <c r="I361" s="23" t="inlineStr"/>
       <c r="J361" s="23" t="inlineStr"/>
-      <c r="K361" s="32" t="n"/>
-      <c r="L361" s="32" t="inlineStr"/>
+      <c r="K361" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L361" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M361" s="32" t="n"/>
       <c r="N361" s="38" t="inlineStr">
         <is>
@@ -17508,11 +20284,23 @@
       <c r="E362" s="23" t="inlineStr"/>
       <c r="F362" s="23" t="inlineStr"/>
       <c r="G362" s="23" t="inlineStr"/>
-      <c r="H362" s="23" t="inlineStr"/>
+      <c r="H362" s="23" t="inlineStr">
+        <is>
+          <t>60,130</t>
+        </is>
+      </c>
       <c r="I362" s="23" t="inlineStr"/>
       <c r="J362" s="23" t="inlineStr"/>
-      <c r="K362" s="32" t="n"/>
-      <c r="L362" s="32" t="inlineStr"/>
+      <c r="K362" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L362" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M362" s="32" t="n"/>
       <c r="N362" s="32" t="n"/>
       <c r="O362" s="23" t="inlineStr"/>
@@ -17555,11 +20343,23 @@
       <c r="E363" s="23" t="inlineStr"/>
       <c r="F363" s="23" t="inlineStr"/>
       <c r="G363" s="23" t="inlineStr"/>
-      <c r="H363" s="23" t="inlineStr"/>
+      <c r="H363" s="23" t="inlineStr">
+        <is>
+          <t>6,040,603</t>
+        </is>
+      </c>
       <c r="I363" s="23" t="inlineStr"/>
       <c r="J363" s="23" t="inlineStr"/>
-      <c r="K363" s="32" t="n"/>
-      <c r="L363" s="32" t="inlineStr"/>
+      <c r="K363" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L363" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M363" s="7" t="inlineStr">
         <is>
           <t>HUB. Excision 55x, Paper Diamond 49x, Keys N Krates 43x, Gramatik 43x, Dillon Francis 43x - none from this project</t>
@@ -17610,11 +20410,23 @@
       <c r="E364" s="23" t="inlineStr"/>
       <c r="F364" s="23" t="inlineStr"/>
       <c r="G364" s="23" t="inlineStr"/>
-      <c r="H364" s="23" t="inlineStr"/>
+      <c r="H364" s="23" t="inlineStr">
+        <is>
+          <t>106,909</t>
+        </is>
+      </c>
       <c r="I364" s="23" t="inlineStr"/>
       <c r="J364" s="23" t="inlineStr"/>
-      <c r="K364" s="32" t="n"/>
-      <c r="L364" s="32" t="inlineStr"/>
+      <c r="K364" s="32" t="inlineStr">
+        <is>
+          <t>measured 2026-08-05</t>
+        </is>
+      </c>
+      <c r="L364" s="28" t="inlineStr">
+        <is>
+          <t>Above - booking is not currency at this size</t>
+        </is>
+      </c>
       <c r="M364" s="7" t="inlineStr">
         <is>
           <t>HUB. Subtronics 93x, Ganja White Night 91x, SubDocta 64x, Dirt Monkey 61x, SoDown 53x</t>
@@ -17668,7 +20480,11 @@
       <c r="H365" s="23" t="inlineStr"/>
       <c r="I365" s="23" t="inlineStr"/>
       <c r="J365" s="23" t="inlineStr"/>
-      <c r="K365" s="32" t="n"/>
+      <c r="K365" s="32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS - D&amp;B artist, name collides. NOT measured</t>
+        </is>
+      </c>
       <c r="L365" s="32" t="inlineStr"/>
       <c r="M365" s="32" t="n"/>
       <c r="N365" s="32" t="n"/>
